--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$73</definedName>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -5012,7 +5012,7 @@
         <v>375</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>330</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>да: 206 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>да: 104 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>да: 295 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -826,12 +826,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 259 м</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>да: 200 м</t>
+          <t>да: 213 м</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2594,7 +2594,7 @@
         <v>620</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>да: 123 м</t>
+          <t>да: 265 м</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5638,7 +5638,7 @@
         <v>361</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>да: 23 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 206 м</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6448,7 +6448,7 @@
         <v>321</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>да: 175 м</t>
+          <t>да: 199 м</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 104 м</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 295 м</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 419 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3801,61 +3801,61 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Абдурауфа Фитрата, 28</t>
+          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>41.271606</v>
+        <v>41.3704</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>69.30528200000001</v>
+        <v>69.303775</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>41.271606, 69.305282</t>
+          <t>41.370400, 69.303775</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271606,69.305282</t>
+          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>да: 265 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -3891,61 +3891,61 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Бешагач махалля</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>41.3704</v>
+        <v>41.304152</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>69.303775</v>
+        <v>69.24776199999999</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>41.370400, 69.303775</t>
+          <t>41.304152, 69.247762</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
+          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 1 м</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -3959,11 +3959,11 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3988,33 +3988,33 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Бешагач махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.304152</v>
+        <v>41.320524</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>69.24776199999999</v>
+        <v>69.326745</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41.304152, 69.247762</t>
+          <t>41.320524, 69.326745</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
+          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>да: 87 м</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4078,33 +4078,33 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
+          <t>Ташкент,   3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41.320524</v>
+        <v>41.285129</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>69.326745</v>
+        <v>69.21448700000001</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>41.320524, 69.326745</t>
+          <t>41.285129, 69.214487</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
+          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>да: 87 м</t>
+          <t>да: 109 м</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4161,61 +4161,61 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Ташкент,   3</t>
+          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41.285129</v>
+        <v>41.272864</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>69.21448700000001</v>
+        <v>69.24437</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>41.285129, 69.214487</t>
+          <t>41.272864, 69.244370</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
+          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>да: 109 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4251,61 +4251,61 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Чиланзар-25</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>41.272864</v>
+        <v>41.28283</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>69.24437</v>
+        <v>69.169132</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.272864, 69.244370</t>
+          <t>41.282830, 69.169132</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
+          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4338,43 +4338,43 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
+          <t>Ташкент, Асака ул., 50-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Чиланзар-25</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41.28283</v>
+        <v>41.315832</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>69.169132</v>
+        <v>69.303838</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>41.282830, 69.169132</t>
+          <t>41.315832, 69.303838</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
+          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 81 м</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4428,55 +4428,55 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ташкент, Асака ул., 50-5</t>
+          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Юнусабад-6</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41.315832</v>
+        <v>41.3711</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>69.303838</v>
+        <v>69.26542600000001</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41.315832, 69.303838</t>
+          <t>41.371100, 69.265426</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
+          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>да: 81 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -4521,14 +4521,14 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
+          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4538,39 +4538,39 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Юнусабад-6</t>
+          <t>Алай (Ц-2)</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41.3711</v>
+        <v>41.31665</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>69.26542600000001</v>
+        <v>69.283869</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>41.371100, 69.265426</t>
+          <t>41.316650, 69.283869</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
+          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4618,33 +4618,33 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Алай (Ц-2)</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>41.31665</v>
+        <v>41.351161</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>69.283869</v>
+        <v>69.23766000000001</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.316650, 69.283869</t>
+          <t>41.351161, 69.237660</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
+          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4653,19 +4653,19 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 13 м</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4708,33 +4708,29 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Абу Али ибн Сино-1</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41.351161</v>
+        <v>41.334773</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>69.23766000000001</v>
+        <v>69.164872</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41.351161, 69.237660</t>
+          <t>41.334773, 69.164872</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
+          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4743,19 +4739,19 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>да: 13 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4773,7 +4769,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4798,29 +4794,33 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>Ташкент, 26-Й Квартал 30</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Абу Али ибн Сино-1</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41.334773</v>
+        <v>41.274511</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>69.164872</v>
+        <v>69.174975</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>41.334773, 69.164872</t>
+          <t>41.274511, 69.174975</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
+          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4829,14 +4829,14 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4855,11 +4855,11 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4884,33 +4884,33 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ташкент, 26-Й Квартал 30</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Юнусабад-8</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>41.274511</v>
+        <v>41.368767</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>69.174975</v>
+        <v>69.27860200000001</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>41.274511, 69.174975</t>
+          <t>41.368767, 69.278602</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
+          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 120 м</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 375 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4967,52 +4967,48 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Юнусабадский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Ташкент, массив Караташ, 6</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Юнусабад-8</t>
+          <t>Эшангузар махалля</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>41.368767</v>
+        <v>41.317051</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>69.27860200000001</v>
+        <v>69.232038</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>41.368767, 69.278602</t>
+          <t>41.317051, 69.232038</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
+          <t>https://www.google.com/maps?q=41.317051,69.232038</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R51" t="n">
         <v>375</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5021,7 +5017,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>да: 120 м</t>
+          <t>да: 35 м</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5039,12 +5035,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 375 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5054,60 +5050,64 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, массив Караташ, 6</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>массив Чиланзар, 14-й кв-л, 25</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Эшангузар махалля</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41.317051</v>
+        <v>41.297736</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>69.232038</v>
+        <v>69.19082899999999</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>41.317051, 69.232038</t>
+          <t>41.297736, 69.190829</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317051,69.232038</t>
+          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>да: 35 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5140,43 +5140,43 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>массив Чиланзар, 14-й кв-л, 25</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>41.297736</v>
+        <v>41.344107</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>69.19082899999999</v>
+        <v>69.209092</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>41.297736, 69.190829</t>
+          <t>41.344107, 69.209092</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
+          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5185,19 +5185,19 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5240,33 +5240,33 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41.344107</v>
+        <v>41.295273</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>69.209092</v>
+        <v>69.35441400000001</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>41.344107, 69.209092</t>
+          <t>41.295273, 69.354414</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
+          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5275,19 +5275,19 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 23 м</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5320,17 +5320,17 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
+          <t>Ташкент, улица Катта Олмос, 21</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5340,35 +5340,35 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Алмаслык</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41.295273</v>
+        <v>41.271981</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>69.35441400000001</v>
+        <v>69.368154</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>41.295273, 69.354414</t>
+          <t>41.271981, 69.368154</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
+          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>да: 23 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -5410,55 +5410,55 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ташкент, улица Катта Олмос, 21</t>
+          <t>Ташкент Малая Кольцевая Дорога 19</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Алмаслык</t>
+          <t>Чимбай махалля</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41.271981</v>
+        <v>41.3491</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>69.368154</v>
+        <v>69.216686</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>41.271981, 69.368154</t>
+          <t>41.349100, 69.216686</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
+          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5503,61 +5503,61 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ташкент Малая Кольцевая Дорога 19</t>
+          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Чимбай махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>41.3491</v>
+        <v>41.284162</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>69.216686</v>
+        <v>69.35999099999999</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>41.349100, 69.216686</t>
+          <t>41.284162, 69.359991</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
+          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -5593,61 +5593,61 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Чиланзар-16</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>41.284162</v>
+        <v>41.272128</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>69.35999099999999</v>
+        <v>69.200819</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>41.284162, 69.359991</t>
+          <t>41.272128, 69.200819</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
+          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 163 м</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5661,11 +5661,11 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 353 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5690,45 +5690,45 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Ташкент, Абдурауфа Фитрата ул., 13</t>
+          <t>Ташкент, 2-й квартал, 18</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Тузель-2</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41.271454</v>
+        <v>41.291661</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>69.30747700000001</v>
+        <v>69.36116</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>41.271454, 69.307477</t>
+          <t>41.291661, 69.361160</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271454,69.307477</t>
+          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -5773,52 +5773,52 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
+          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Чиланзар-16</t>
+          <t>Чигатай-Актепа махалля</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41.272128</v>
+        <v>41.349977</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>69.200819</v>
+        <v>69.190336</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>41.272128, 69.200819</t>
+          <t>41.349977, 69.190336</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
+          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>да: 163 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -5860,55 +5860,55 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ташкент, 2-й квартал, 18</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Тузель-2</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41.291661</v>
+        <v>41.337068</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>69.36116</v>
+        <v>69.285428</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>41.291661, 69.361160</t>
+          <t>41.337068, 69.285428</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
+          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 46 м</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -5953,49 +5953,49 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа махалля</t>
+          <t>Риёзи (Чизельный)</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>41.349977</v>
+        <v>41.314418</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>69.190336</v>
+        <v>69.32381700000001</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>41.349977, 69.190336</t>
+          <t>41.314418, 69.323817</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
+          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 142 м</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6050,33 +6050,33 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Минор (Ц-6)</t>
+          <t>Геофизика</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41.337068</v>
+        <v>41.338894</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>69.285428</v>
+        <v>69.386939</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>41.337068, 69.285428</t>
+          <t>41.338894, 69.386939</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
+          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>да: 46 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6133,52 +6133,52 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>Сергели</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>41.314418</v>
+        <v>41.214477</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>69.32381700000001</v>
+        <v>69.212414</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>41.314418, 69.323817</t>
+          <t>41.214477, 69.212414</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>да: 142 м</t>
+          <t>да: 206 м</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6230,33 +6230,33 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Геофизика</t>
+          <t>Куйлюк Центр</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41.338894</v>
+        <v>41.24192</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>69.386939</v>
+        <v>69.33096</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>41.338894, 69.386939</t>
+          <t>41.241920, 69.330960</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 199 м</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6291,16 +6291,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -6310,55 +6310,55 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+          <t>Ташкент, массив Аханграбо, 8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Сергели</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41.214477</v>
+        <v>41.252678</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>69.212414</v>
+        <v>69.344067</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>41.214477, 69.212414</t>
+          <t>41.252678, 69.344067</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>да: 206 м</t>
+          <t>да: 104 м</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -6400,55 +6400,55 @@
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Чиланзар-18</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41.24192</v>
+        <v>41.274182</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>69.33096</v>
+        <v>69.190247</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>41.241920, 69.330960</t>
+          <t>41.274182, 69.190247</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>да: 199 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6490,43 +6490,43 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ташкент, массив Аханграбо, 8</t>
+          <t>Ташкент, 8-Й Квартал 1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Чиланзар-6</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>41.252678</v>
+        <v>41.287081</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>69.344067</v>
+        <v>69.205814</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>41.252678, 69.344067</t>
+          <t>41.287081, 69.205814</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>да: 104 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -6580,55 +6580,55 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
+          <t>Ташкент, улица Буюк Ипак Йули 77</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Чиланзар-18</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>41.274182</v>
+        <v>41.326369</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>69.190247</v>
+        <v>69.32475700000001</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>41.274182, 69.190247</t>
+          <t>41.326369, 69.324757</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
+          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6680,33 +6680,33 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Ташкент, 8-Й Квартал 1</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Чиланзар-6</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>41.287081</v>
+        <v>41.235793</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>69.205814</v>
+        <v>69.352153</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>41.287081, 69.205814</t>
+          <t>41.235793, 69.352153</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 295 м</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -6763,52 +6763,48 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Ташкент, улица Буюк Ипак Йули 77</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Мирзо Улугбекский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Сергели-6А</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>41.326369</v>
+        <v>41.230149</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>69.32475700000001</v>
+        <v>69.206614</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>41.326369, 69.324757</t>
+          <t>41.230149, 69.206614</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R71" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6817,7 +6813,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 9 м</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -6826,184 +6822,8 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="n">
-        <v>20</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Wildberries</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Бузаучи</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>41.235793</v>
-      </c>
-      <c r="N72" s="2" t="n">
-        <v>69.352153</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>41.235793, 69.352153</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R72" t="n">
-        <v>306</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>да: 295 м</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="n">
-        <v>20</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Яндекс Маркет</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Сергели-6А</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>41.230149</v>
-      </c>
-      <c r="N73" s="2" t="n">
-        <v>69.206614</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>41.230149, 69.206614</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R73" t="n">
-        <v>302</v>
-      </c>
-      <c r="S73" t="n">
-        <v>8</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>да: 9 м</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V73"/>
+  <autoFilter ref="A1:V71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -826,12 +826,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>да: 259 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>да: 139 м</t>
+          <t>да: 269 м</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 224 м</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 18 м</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>да: 291 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 112 м</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>да: 109 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 299 м</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>да: 81 м</t>
+          <t>да: 86 м</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>да: 35 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 283 м</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>да: 23 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>да: 163 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>да: 142 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>да: 206 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>да: 199 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2797,11 +2797,11 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 579 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 477 м</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>579</v>
+        <v>477</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 435 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3089,61 +3089,57 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Ташкент, проспект Амира Темура, 51</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Мирабадский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Зафарабад махалля</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>41.296327</v>
+        <v>41.34016</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>69.28720199999999</v>
+        <v>69.199088</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>41.296327, 69.287202</t>
+          <t>41.340160, 69.199088</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.296327,69.287202</t>
+          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>да: 112 м</t>
+          <t>да: 164 м</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3186,29 +3182,33 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Зафарабад махалля</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41.34016</v>
+        <v>41.295637</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>69.199088</v>
+        <v>69.331536</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>41.340160, 69.199088</t>
+          <t>41.295637, 69.331536</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
+          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>да: 164 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3272,33 +3272,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41.295637</v>
+        <v>41.228417</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>69.331536</v>
+        <v>69.328615</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.295637, 69.331536</t>
+          <t>41.228417, 69.328615</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
+          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3307,19 +3307,19 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3362,33 +3362,33 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
+          <t>Ташкент,   51</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>ТТЗ-2</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41.228417</v>
+        <v>41.357678</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>69.328615</v>
+        <v>69.383498</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>41.228417, 69.328615</t>
+          <t>41.357678, 69.383498</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
+          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3452,33 +3452,33 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ташкент,   51</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ТТЗ-2</t>
+          <t>Каракамыш 2/3</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41.357678</v>
+        <v>41.370139</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>69.383498</v>
+        <v>69.215407</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>41.357678, 69.383498</t>
+          <t>41.370139, 69.215407</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
+          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3542,33 +3542,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Каракамыш 2/3</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41.370139</v>
+        <v>41.279926</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>69.215407</v>
+        <v>69.181485</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>41.370139, 69.215407</t>
+          <t>41.279926, 69.181485</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
+          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3632,33 +3632,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Учтепинский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Сергели-8</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41.279926</v>
+        <v>41.221246</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>69.181485</v>
+        <v>69.222719</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>41.279926, 69.181485</t>
+          <t>41.221246, 69.222719</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
+          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3667,19 +3663,19 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3697,12 +3693,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3715,57 +3711,61 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Юнусабадский район</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Сергели-8</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>41.221246</v>
+        <v>41.3704</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>69.222719</v>
+        <v>69.303775</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>41.221246, 69.222719</t>
+          <t>41.370400, 69.303775</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
+          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3801,61 +3801,61 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Бешагач махалля</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>41.3704</v>
+        <v>41.304152</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>69.303775</v>
+        <v>69.24776199999999</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>41.370400, 69.303775</t>
+          <t>41.304152, 69.247762</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
+          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 1 м</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3869,11 +3869,11 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3898,33 +3898,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Бешагач махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>41.304152</v>
+        <v>41.320524</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>69.24776199999999</v>
+        <v>69.326745</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>41.304152, 69.247762</t>
+          <t>41.320524, 69.326745</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
+          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>да: 87 м</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3988,33 +3988,33 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
+          <t>Ташкент,   3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.320524</v>
+        <v>41.285129</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>69.326745</v>
+        <v>69.21448700000001</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41.320524, 69.326745</t>
+          <t>41.285129, 69.214487</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
+          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>да: 87 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4071,52 +4071,52 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ташкент,   3</t>
+          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41.285129</v>
+        <v>41.272864</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>69.21448700000001</v>
+        <v>69.24437</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>41.285129, 69.214487</t>
+          <t>41.272864, 69.244370</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
+          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 299 м</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4161,52 +4161,52 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Чиланзар-25</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41.272864</v>
+        <v>41.28283</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>69.24437</v>
+        <v>69.169132</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>41.272864, 69.244370</t>
+          <t>41.282830, 69.169132</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
+          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>да: 299 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4248,43 +4248,43 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
+          <t>Ташкент, Асака ул., 50-5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Чиланзар-25</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>41.28283</v>
+        <v>41.315832</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>69.169132</v>
+        <v>69.303838</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.282830, 69.169132</t>
+          <t>41.315832, 69.303838</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
+          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 86 м</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4338,55 +4338,55 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ташкент, Асака ул., 50-5</t>
+          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Юнусабад-6</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41.315832</v>
+        <v>41.3711</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>69.303838</v>
+        <v>69.26542600000001</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>41.315832, 69.303838</t>
+          <t>41.371100, 69.265426</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
+          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>да: 86 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4431,14 +4431,14 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
+          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4448,35 +4448,35 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Юнусабад-6</t>
+          <t>Алай (Ц-2)</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41.3711</v>
+        <v>41.31665</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>69.26542600000001</v>
+        <v>69.283869</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41.371100, 69.265426</t>
+          <t>41.316650, 69.283869</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
+          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4528,33 +4528,33 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Алай (Ц-2)</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41.31665</v>
+        <v>41.351161</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>69.283869</v>
+        <v>69.23766000000001</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>41.316650, 69.283869</t>
+          <t>41.351161, 69.237660</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
+          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 13 м</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4618,33 +4618,29 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Абу Али ибн Сино-1</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>41.351161</v>
+        <v>41.334773</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>69.23766000000001</v>
+        <v>69.164872</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.351161, 69.237660</t>
+          <t>41.334773, 69.164872</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
+          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4653,19 +4649,19 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>да: 13 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4683,7 +4679,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4708,29 +4704,33 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Ташкент, 26-Й Квартал 30</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Абу Али ибн Сино-1</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41.334773</v>
+        <v>41.274511</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>69.164872</v>
+        <v>69.174975</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41.334773, 69.164872</t>
+          <t>41.274511, 69.174975</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
+          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4739,14 +4739,14 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4765,11 +4765,11 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4794,33 +4794,33 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ташкент, 26-Й Квартал 30</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Юнусабад-8</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41.274511</v>
+        <v>41.368767</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>69.174975</v>
+        <v>69.27860200000001</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>41.274511, 69.174975</t>
+          <t>41.368767, 69.278602</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
+          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 120 м</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 375 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4877,52 +4877,48 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Юнусабадский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Ташкент, массив Караташ, 6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Юнусабад-8</t>
+          <t>Эшангузар махалля</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>41.368767</v>
+        <v>41.317051</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>69.27860200000001</v>
+        <v>69.232038</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>41.368767, 69.278602</t>
+          <t>41.317051, 69.232038</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
+          <t>https://www.google.com/maps?q=41.317051,69.232038</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R50" t="n">
         <v>375</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4931,7 +4927,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>да: 120 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -4949,12 +4945,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 375 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4964,51 +4960,55 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, массив Караташ, 6</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>массив Чиланзар, 14-й кв-л, 25</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Эшангузар махалля</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>41.317051</v>
+        <v>41.297736</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>69.232038</v>
+        <v>69.19082899999999</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>41.317051, 69.232038</t>
+          <t>41.297736, 69.190829</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317051,69.232038</t>
+          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5035,12 +5035,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5050,43 +5050,43 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>массив Чиланзар, 14-й кв-л, 25</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41.297736</v>
+        <v>41.344107</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>69.19082899999999</v>
+        <v>69.209092</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>41.297736, 69.190829</t>
+          <t>41.344107, 69.209092</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
+          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 283 м</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5150,33 +5150,33 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>41.344107</v>
+        <v>41.295273</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>69.209092</v>
+        <v>69.35441400000001</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>41.344107, 69.209092</t>
+          <t>41.295273, 69.354414</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
+          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>да: 283 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5230,17 +5230,17 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
+          <t>Ташкент, улица Катта Олмос, 21</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5250,35 +5250,35 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Алмаслык</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41.295273</v>
+        <v>41.271981</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>69.35441400000001</v>
+        <v>69.368154</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>41.295273, 69.354414</t>
+          <t>41.271981, 69.368154</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
+          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5320,55 +5320,55 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Ташкент, улица Катта Олмос, 21</t>
+          <t>Ташкент Малая Кольцевая Дорога 19</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Алмаслык</t>
+          <t>Чимбай махалля</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41.271981</v>
+        <v>41.3491</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>69.368154</v>
+        <v>69.216686</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>41.271981, 69.368154</t>
+          <t>41.349100, 69.216686</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
+          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -5413,52 +5413,52 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ташкент Малая Кольцевая Дорога 19</t>
+          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Чимбай махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41.3491</v>
+        <v>41.284162</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>69.216686</v>
+        <v>69.35999099999999</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>41.349100, 69.216686</t>
+          <t>41.284162, 69.359991</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
+          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5503,52 +5503,52 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Чиланзар-16</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>41.284162</v>
+        <v>41.272128</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>69.35999099999999</v>
+        <v>69.200819</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>41.284162, 69.359991</t>
+          <t>41.272128, 69.200819</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
+          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5571,16 +5571,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -5590,52 +5590,52 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
+          <t>Ташкент, 2-й квартал, 18</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Чиланзар-16</t>
+          <t>Тузель-2</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>41.272128</v>
+        <v>41.291661</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>69.200819</v>
+        <v>69.36116</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>41.272128, 69.200819</t>
+          <t>41.291661, 69.361160</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
+          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -5665,12 +5665,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -5680,43 +5680,43 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Ташкент, 2-й квартал, 18</t>
+          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Тузель-2</t>
+          <t>Чигатай-Актепа махалля</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41.291661</v>
+        <v>41.349977</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>69.36116</v>
+        <v>69.190336</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>41.291661, 69.361160</t>
+          <t>41.349977, 69.190336</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
+          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -5773,49 +5773,49 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа махалля</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41.349977</v>
+        <v>41.337068</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>69.190336</v>
+        <v>69.285428</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>41.349977, 69.190336</t>
+          <t>41.337068, 69.285428</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
+          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 46 м</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5870,33 +5870,33 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Минор (Ц-6)</t>
+          <t>Риёзи (Чизельный)</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41.337068</v>
+        <v>41.314418</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>69.285428</v>
+        <v>69.32381700000001</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>41.337068, 69.285428</t>
+          <t>41.314418, 69.323817</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
+          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>да: 46 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5960,33 +5960,33 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>Геофизика</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>41.314418</v>
+        <v>41.338894</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>69.32381700000001</v>
+        <v>69.386939</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>41.314418, 69.323817</t>
+          <t>41.338894, 69.386939</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6025,12 +6025,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6043,52 +6043,52 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Геофизика</t>
+          <t>Сергели</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41.338894</v>
+        <v>41.214477</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>69.386939</v>
+        <v>69.212414</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>41.338894, 69.386939</t>
+          <t>41.214477, 69.212414</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6133,52 +6133,52 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Сергели</t>
+          <t>Куйлюк Центр</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>41.214477</v>
+        <v>41.24192</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>69.212414</v>
+        <v>69.33096</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>41.214477, 69.212414</t>
+          <t>41.241920, 69.330960</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6201,16 +6201,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6220,17 +6220,17 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+          <t>Ташкент, массив Аханграбо, 8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6240,23 +6240,23 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41.24192</v>
+        <v>41.252678</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>69.33096</v>
+        <v>69.344067</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>41.241920, 69.330960</t>
+          <t>41.252678, 69.344067</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 104 м</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6320,45 +6320,45 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ташкент, массив Аханграбо, 8</t>
+          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Чиланзар-18</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41.252678</v>
+        <v>41.274182</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>69.344067</v>
+        <v>69.190247</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>41.252678, 69.344067</t>
+          <t>41.274182, 69.190247</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>да: 104 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -6400,17 +6400,17 @@
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
+          <t>Ташкент, 8-Й Квартал 1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6420,35 +6420,35 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Чиланзар-18</t>
+          <t>Чиланзар-6</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41.274182</v>
+        <v>41.287081</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>69.190247</v>
+        <v>69.205814</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>41.274182, 69.190247</t>
+          <t>41.287081, 69.205814</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
+          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6500,33 +6500,33 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ташкент, 8-Й Квартал 1</t>
+          <t>Ташкент, улица Буюк Ипак Йули 77</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Чиланзар-6</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>41.287081</v>
+        <v>41.326369</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>69.205814</v>
+        <v>69.32475700000001</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>41.287081, 69.205814</t>
+          <t>41.326369, 69.324757</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6590,33 +6590,33 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Ташкент, улица Буюк Ипак Йули 77</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>41.326369</v>
+        <v>41.235793</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>69.32475700000001</v>
+        <v>69.352153</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>41.326369, 69.324757</t>
+          <t>41.235793, 69.352153</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 295 м</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -6673,52 +6673,48 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Сергели-6А</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>41.235793</v>
+        <v>41.230149</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>69.352153</v>
+        <v>69.206614</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>41.235793, 69.352153</t>
+          <t>41.230149, 69.206614</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
+          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6727,7 +6723,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>да: 295 м</t>
+          <t>да: 9 м</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6736,94 +6732,8 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="n">
-        <v>20</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Яндекс Маркет</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Сергели-6А</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>41.230149</v>
-      </c>
-      <c r="N71" s="2" t="n">
-        <v>69.206614</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>41.230149, 69.206614</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R71" t="n">
-        <v>302</v>
-      </c>
-      <c r="S71" t="n">
-        <v>8</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>да: 9 м</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V71"/>
+  <autoFilter ref="A1:V70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 751 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 737 м</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1852,29 +1852,33 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтинводий, 11</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, 2-й пр-д Боситхон, 32</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Венгерская</t>
+          <t>Урикзар</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>41.260607</v>
+        <v>41.286849</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>69.249556</v>
+        <v>69.143169</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>41.260607, 69.249556</t>
+          <t>41.286849, 69.143169</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.260607,69.249556</t>
+          <t>https://www.google.com/maps?q=41.286849,69.143169</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1883,19 +1887,19 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>да: 213 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1909,11 +1913,11 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 737 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 732 м</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1938,33 +1942,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 2-й пр-д Боситхон, 32</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Учтепинский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Кумарык, 32</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Урикзар</t>
+          <t>Кумарык махалля</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>41.286849</v>
+        <v>41.249946</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>69.143169</v>
+        <v>69.25695899999999</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>41.286849, 69.143169</t>
+          <t>41.249946, 69.256959</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286849,69.143169</t>
+          <t>https://www.google.com/maps?q=41.249946,69.256959</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1973,19 +1973,19 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 732 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 712 м</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2028,29 +2028,33 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Кумарык, 32</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Ташкент, массив Сувсоз-2 29</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Бектемирский район</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Кумарык махалля</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>41.249946</v>
+        <v>41.254455</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>69.25695899999999</v>
+        <v>69.376133</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41.249946, 69.256959</t>
+          <t>41.254455, 69.376133</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.249946,69.256959</t>
+          <t>https://www.google.com/maps?q=41.254455,69.376133</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2059,19 +2063,19 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 224 м</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2089,12 +2093,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 712 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 708 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2107,61 +2111,61 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Ташкент, массив Сувсоз-2 29</t>
+          <t>Ташкент, Ташкент, улица Фараби, 28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Вузгородок</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>41.254455</v>
+        <v>41.346828</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>69.376133</v>
+        <v>69.205709</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>41.254455, 69.376133</t>
+          <t>41.346828, 69.205709</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254455,69.376133</t>
+          <t>https://www.google.com/maps?q=41.346828,69.205709</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>да: 224 м</t>
+          <t>да: 66 м</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2175,16 +2179,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 708 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 699 м</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2197,61 +2201,57 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 28</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Алишера Навои, 26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Вузгородок</t>
+          <t>Хадра (Ц-14)</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>41.346828</v>
+        <v>41.321559</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>69.205709</v>
+        <v>69.253536</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>41.346828, 69.205709</t>
+          <t>41.321559, 69.253536</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.346828,69.205709</t>
+          <t>https://www.google.com/maps?q=41.321559,69.253536</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>да: 66 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2265,11 +2265,11 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 699 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 664 м</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2294,29 +2294,29 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Алишера Навои, 26</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Чаштепа, 31</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Хадра (Ц-14)</t>
+          <t>ЖК "Домбрабад Тауерс"</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>41.321559</v>
+        <v>41.248641</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>69.253536</v>
+        <v>69.210115</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>41.321559, 69.253536</t>
+          <t>41.248641, 69.210115</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.321559,69.253536</t>
+          <t>https://www.google.com/maps?q=41.248641,69.210115</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>699</v>
+        <v>664</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2351,11 +2351,11 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 664 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 622 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2380,50 +2380,54 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Чаштепа, 31</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Ташкент,   15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Алмазарский район</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ЖК "Домбрабад Тауерс"</t>
+          <t>Чукурсай</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>41.248641</v>
+        <v>41.369273</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>69.210115</v>
+        <v>69.230796</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>41.248641, 69.210115</t>
+          <t>41.369273, 69.230796</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.248641,69.210115</t>
+          <t>https://www.google.com/maps?q=41.369273,69.230796</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>664</v>
+        <v>622</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 77 м</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2441,7 +2445,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 622 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 620 м</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2466,45 +2470,45 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ташкент,   15</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Катта Янгиабад, 7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Чукурсай</t>
+          <t>Надыра махалля</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>41.369273</v>
+        <v>41.27502</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>69.230796</v>
+        <v>69.350781</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>41.369273, 69.230796</t>
+          <t>41.275020, 69.350781</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.369273,69.230796</t>
+          <t>https://www.google.com/maps?q=41.275020,69.350781</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2513,7 +2517,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>да: 77 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2527,11 +2531,11 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 620 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 603 м</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2556,33 +2560,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Катта Янгиабад, 7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 4-й пр-д Мингурик, 3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Надыра махалля</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41.27502</v>
+        <v>41.342982</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>69.350781</v>
+        <v>69.300478</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>41.275020, 69.350781</t>
+          <t>41.342982, 69.300478</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.275020,69.350781</t>
+          <t>https://www.google.com/maps?q=41.342982,69.300478</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2591,19 +2595,19 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 18 м</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2621,12 +2625,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 603 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 586 м</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2636,43 +2640,43 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 4-й пр-д Мингурик, 3</t>
+          <t>Ташкент, Иззат ул., 58/4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>41.342982</v>
+        <v>41.272995</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>69.300478</v>
+        <v>69.340649</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>41.342982, 69.300478</t>
+          <t>41.272995, 69.340649</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.342982,69.300478</t>
+          <t>https://www.google.com/maps?q=41.272995,69.340649</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2681,10 +2685,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2693,7 +2697,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>да: 18 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2707,11 +2711,11 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 586 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 477 м</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2736,33 +2740,33 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ташкент, Иззат ул., 58/4</t>
+          <t>Ташкент, Туркистан ул., 12</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>41.272995</v>
+        <v>41.292276</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>69.340649</v>
+        <v>69.285268</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>41.272995, 69.340649</t>
+          <t>41.292276, 69.285268</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272995,69.340649</t>
+          <t>https://www.google.com/maps?q=41.292276,69.285268</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2771,19 +2775,19 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>586</v>
+        <v>477</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2797,16 +2801,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 477 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2816,64 +2820,64 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ташкент, Туркистан ул., 12</t>
+          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>41.292276</v>
+        <v>41.209344</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>69.285268</v>
+        <v>69.20008300000001</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>41.292276, 69.285268</t>
+          <t>41.209344, 69.200083</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.292276,69.285268</t>
+          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 64 м</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2891,7 +2895,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2916,33 +2920,33 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
+          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>41.209344</v>
+        <v>41.290617</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>69.20008300000001</v>
+        <v>69.355688</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>41.209344, 69.200083</t>
+          <t>41.290617, 69.355688</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
+          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2951,19 +2955,19 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>да: 64 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -2977,16 +2981,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2999,61 +3003,57 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Яшнободский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Зафарабад махалля</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41.290617</v>
+        <v>41.34016</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>69.355688</v>
+        <v>69.199088</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>41.290617, 69.355688</t>
+          <t>41.340160, 69.199088</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
+          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 164 м</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3096,29 +3096,33 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Зафарабад махалля</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>41.34016</v>
+        <v>41.295637</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>69.199088</v>
+        <v>69.331536</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>41.340160, 69.199088</t>
+          <t>41.295637, 69.331536</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
+          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3134,12 +3138,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>да: 164 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3157,7 +3161,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3182,33 +3186,33 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41.295637</v>
+        <v>41.228417</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>69.331536</v>
+        <v>69.328615</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>41.295637, 69.331536</t>
+          <t>41.228417, 69.328615</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
+          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3217,19 +3221,19 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3247,7 +3251,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3272,33 +3276,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
+          <t>Ташкент,   51</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>ТТЗ-2</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41.228417</v>
+        <v>41.357678</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>69.328615</v>
+        <v>69.383498</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.228417, 69.328615</t>
+          <t>41.357678, 69.383498</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
+          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3307,10 +3311,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3362,33 +3366,33 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ташкент,   51</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ТТЗ-2</t>
+          <t>Каракамыш 2/3</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41.357678</v>
+        <v>41.370139</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>69.383498</v>
+        <v>69.215407</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>41.357678, 69.383498</t>
+          <t>41.370139, 69.215407</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
+          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3427,7 +3431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3452,33 +3456,33 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Каракамыш 2/3</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41.370139</v>
+        <v>41.279926</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>69.215407</v>
+        <v>69.181485</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>41.370139, 69.215407</t>
+          <t>41.279926, 69.181485</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
+          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3487,19 +3491,19 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3517,7 +3521,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3542,33 +3546,29 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Учтепинский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Сергели-8</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41.279926</v>
+        <v>41.221246</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>69.181485</v>
+        <v>69.222719</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>41.279926, 69.181485</t>
+          <t>41.221246, 69.222719</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
+          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3625,57 +3625,61 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Юнусабадский район</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Сергели-8</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41.221246</v>
+        <v>41.3704</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>69.222719</v>
+        <v>69.303775</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>41.221246, 69.222719</t>
+          <t>41.370400, 69.303775</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
+          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3693,12 +3697,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -3711,61 +3715,61 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Бешагач махалля</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>41.3704</v>
+        <v>41.304152</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>69.303775</v>
+        <v>69.24776199999999</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>41.370400, 69.303775</t>
+          <t>41.304152, 69.247762</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
+          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 1 м</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3779,11 +3783,11 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3808,33 +3812,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Бешагач махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>41.304152</v>
+        <v>41.320524</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>69.24776199999999</v>
+        <v>69.326745</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>41.304152, 69.247762</t>
+          <t>41.320524, 69.326745</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
+          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3843,10 +3847,10 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3855,7 +3859,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>да: 87 м</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3873,7 +3877,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3898,33 +3902,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
+          <t>Ташкент,   3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>41.320524</v>
+        <v>41.285129</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>69.326745</v>
+        <v>69.21448700000001</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>41.320524, 69.326745</t>
+          <t>41.285129, 69.214487</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
+          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3933,10 +3937,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3945,7 +3949,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>да: 87 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -3963,12 +3967,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3981,52 +3985,52 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Ташкент,   3</t>
+          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.285129</v>
+        <v>41.272864</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>69.21448700000001</v>
+        <v>69.24437</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41.285129, 69.214487</t>
+          <t>41.272864, 69.244370</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
+          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4035,7 +4039,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 299 м</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4053,12 +4057,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4071,52 +4075,52 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Чиланзар-25</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41.272864</v>
+        <v>41.28283</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>69.24437</v>
+        <v>69.169132</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>41.272864, 69.244370</t>
+          <t>41.282830, 69.169132</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
+          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4125,7 +4129,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>да: 299 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4143,12 +4147,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4158,43 +4162,43 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
+          <t>Ташкент, Асака ул., 50-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Чиланзар-25</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41.28283</v>
+        <v>41.315832</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>69.169132</v>
+        <v>69.303838</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>41.282830, 69.169132</t>
+          <t>41.315832, 69.303838</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
+          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4203,10 +4207,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4215,7 +4219,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 86 м</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4233,12 +4237,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4248,55 +4252,55 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ташкент, Асака ул., 50-5</t>
+          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Юнусабад-6</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>41.315832</v>
+        <v>41.3711</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>69.303838</v>
+        <v>69.26542600000001</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.315832, 69.303838</t>
+          <t>41.371100, 69.265426</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
+          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4305,7 +4309,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>да: 86 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4323,12 +4327,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4341,14 +4345,14 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
+          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4358,35 +4362,35 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Юнусабад-6</t>
+          <t>Алай (Ц-2)</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41.3711</v>
+        <v>41.31665</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>69.26542600000001</v>
+        <v>69.283869</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>41.371100, 69.265426</t>
+          <t>41.316650, 69.283869</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
+          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4413,7 +4417,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4438,33 +4442,33 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Алай (Ц-2)</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41.31665</v>
+        <v>41.351161</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>69.283869</v>
+        <v>69.23766000000001</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41.316650, 69.283869</t>
+          <t>41.351161, 69.237660</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
+          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4473,10 +4477,10 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4485,7 +4489,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 13 м</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4503,7 +4507,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4528,33 +4532,29 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Абу Али ибн Сино-1</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41.351161</v>
+        <v>41.334773</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>69.23766000000001</v>
+        <v>69.164872</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>41.351161, 69.237660</t>
+          <t>41.334773, 69.164872</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
+          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4563,19 +4563,19 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>да: 13 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4618,29 +4618,33 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>Ташкент, 26-Й Квартал 30</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Абу Али ибн Сино-1</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>41.334773</v>
+        <v>41.274511</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>69.164872</v>
+        <v>69.174975</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.334773, 69.164872</t>
+          <t>41.274511, 69.174975</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
+          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4649,14 +4653,14 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -4675,11 +4679,11 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4704,33 +4708,33 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ташкент, 26-Й Квартал 30</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Юнусабад-8</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41.274511</v>
+        <v>41.368767</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>69.174975</v>
+        <v>69.27860200000001</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41.274511, 69.174975</t>
+          <t>41.368767, 69.278602</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
+          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4739,10 +4743,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4751,7 +4755,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 120 м</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4769,12 +4773,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4784,43 +4788,43 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
+          <t>массив Чиланзар, 14-й кв-л, 25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Юнусабад-8</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41.368767</v>
+        <v>41.297736</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>69.27860200000001</v>
+        <v>69.19082899999999</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>41.368767, 69.278602</t>
+          <t>41.297736, 69.190829</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
+          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4829,10 +4833,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4841,7 +4845,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>да: 120 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4859,12 +4863,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 375 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4877,48 +4881,52 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, массив Караташ, 6</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Алмазарский район</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Эшангузар махалля</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>41.317051</v>
+        <v>41.344107</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>69.232038</v>
+        <v>69.209092</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>41.317051, 69.232038</t>
+          <t>41.344107, 69.209092</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317051,69.232038</t>
+          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4927,7 +4935,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 283 м</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -4945,12 +4953,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4960,43 +4968,43 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>массив Чиланзар, 14-й кв-л, 25</t>
+          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>41.297736</v>
+        <v>41.295273</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>69.19082899999999</v>
+        <v>69.35441400000001</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>41.297736, 69.190829</t>
+          <t>41.295273, 69.354414</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
+          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5005,10 +5013,10 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5035,12 +5043,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5050,55 +5058,55 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+          <t>Ташкент, улица Катта Олмос, 21</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Алмаслык</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41.344107</v>
+        <v>41.271981</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>69.209092</v>
+        <v>69.368154</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>41.344107, 69.209092</t>
+          <t>41.271981, 69.368154</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
+          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5107,7 +5115,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>да: 283 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5125,7 +5133,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5150,33 +5158,33 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
+          <t>Ташкент Малая Кольцевая Дорога 19</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Чимбай махалля</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>41.295273</v>
+        <v>41.3491</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>69.35441400000001</v>
+        <v>69.216686</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>41.295273, 69.354414</t>
+          <t>41.349100, 69.216686</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
+          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5185,10 +5193,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5197,7 +5205,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5215,12 +5223,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5230,17 +5238,17 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Ташкент, улица Катта Олмос, 21</t>
+          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5250,23 +5258,23 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Алмаслык</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41.271981</v>
+        <v>41.284162</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>69.368154</v>
+        <v>69.35999099999999</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>41.271981, 69.368154</t>
+          <t>41.284162, 69.359991</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
+          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5275,10 +5283,10 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5305,7 +5313,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5330,33 +5338,33 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Ташкент Малая Кольцевая Дорога 19</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Чимбай махалля</t>
+          <t>Чиланзар-16</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41.3491</v>
+        <v>41.272128</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>69.216686</v>
+        <v>69.200819</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>41.349100, 69.216686</t>
+          <t>41.272128, 69.200819</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
+          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5365,10 +5373,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5377,7 +5385,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5391,16 +5399,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -5410,17 +5418,17 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
+          <t>Ташкент, 2-й квартал, 18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5430,23 +5438,23 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Тузель-2</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41.284162</v>
+        <v>41.291661</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>69.35999099999999</v>
+        <v>69.36116</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>41.284162, 69.359991</t>
+          <t>41.291661, 69.361160</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
+          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5455,10 +5463,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5481,16 +5489,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5503,52 +5511,52 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
+          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Чиланзар-16</t>
+          <t>Чигатай-Актепа махалля</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>41.272128</v>
+        <v>41.349977</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>69.200819</v>
+        <v>69.190336</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>41.272128, 69.200819</t>
+          <t>41.349977, 69.190336</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
+          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5575,12 +5583,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -5590,55 +5598,55 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Ташкент, 2-й квартал, 18</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Тузель-2</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>41.291661</v>
+        <v>41.337068</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>69.36116</v>
+        <v>69.285428</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>41.291661, 69.361160</t>
+          <t>41.337068, 69.285428</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
+          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5647,7 +5655,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 46 м</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5665,12 +5673,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -5683,49 +5691,49 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа махалля</t>
+          <t>Риёзи (Чизельный)</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41.349977</v>
+        <v>41.314418</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>69.190336</v>
+        <v>69.32381700000001</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>41.349977, 69.190336</t>
+          <t>41.314418, 69.323817</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
+          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -5755,7 +5763,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5780,33 +5788,33 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Минор (Ц-6)</t>
+          <t>Геофизика</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41.337068</v>
+        <v>41.338894</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>69.285428</v>
+        <v>69.386939</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>41.337068, 69.285428</t>
+          <t>41.338894, 69.386939</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
+          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5815,7 +5823,7 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -5827,7 +5835,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>да: 46 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5845,12 +5853,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -5863,52 +5871,52 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>Сергели</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41.314418</v>
+        <v>41.214477</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>69.32381700000001</v>
+        <v>69.212414</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>41.314418, 69.323817</t>
+          <t>41.214477, 69.212414</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5935,7 +5943,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5960,33 +5968,33 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Геофизика</t>
+          <t>Куйлюк Центр</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>41.338894</v>
+        <v>41.24192</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>69.386939</v>
+        <v>69.33096</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>41.338894, 69.386939</t>
+          <t>41.241920, 69.330960</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5995,7 +6003,7 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -6021,16 +6029,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6040,55 +6048,55 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+          <t>Ташкент, массив Аханграбо, 8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Сергели</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41.214477</v>
+        <v>41.252678</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>69.212414</v>
+        <v>69.344067</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>41.214477, 69.212414</t>
+          <t>41.252678, 69.344067</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6097,7 +6105,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 104 м</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6111,16 +6119,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6130,55 +6138,55 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Чиланзар-18</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>41.24192</v>
+        <v>41.274182</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>69.33096</v>
+        <v>69.190247</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>41.241920, 69.330960</t>
+          <t>41.274182, 69.190247</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6205,12 +6213,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6220,43 +6228,43 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ташкент, массив Аханграбо, 8</t>
+          <t>Ташкент, 8-Й Квартал 1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Чиланзар-6</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41.252678</v>
+        <v>41.287081</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>69.344067</v>
+        <v>69.205814</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>41.252678, 69.344067</t>
+          <t>41.287081, 69.205814</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6265,10 +6273,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6277,7 +6285,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>да: 104 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6295,12 +6303,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -6310,55 +6318,55 @@
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
+          <t>Ташкент, улица Буюк Ипак Йули 77</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Чиланзар-18</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41.274182</v>
+        <v>41.326369</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>69.190247</v>
+        <v>69.32475700000001</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>41.274182, 69.190247</t>
+          <t>41.326369, 69.324757</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
+          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6385,7 +6393,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6410,33 +6418,33 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Ташкент, 8-Й Квартал 1</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Чиланзар-6</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41.287081</v>
+        <v>41.235793</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>69.205814</v>
+        <v>69.352153</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>41.287081, 69.205814</t>
+          <t>41.235793, 69.352153</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6445,10 +6453,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6457,7 +6465,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 295 м</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6475,12 +6483,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6493,52 +6501,48 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ташкент, улица Буюк Ипак Йули 77</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Мирзо Улугбекский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Сергели-6А</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>41.326369</v>
+        <v>41.230149</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>69.32475700000001</v>
+        <v>69.206614</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>41.326369, 69.324757</t>
+          <t>41.230149, 69.206614</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6547,7 +6551,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 9 м</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6556,184 +6560,8 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="n">
-        <v>20</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Wildberries</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Бузаучи</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>41.235793</v>
-      </c>
-      <c r="N69" s="2" t="n">
-        <v>69.352153</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>41.235793, 69.352153</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="R69" t="n">
-        <v>306</v>
-      </c>
-      <c r="S69" t="n">
-        <v>3</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>да: 295 м</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="n">
-        <v>20</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Яндекс Маркет</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Сергели-6А</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>41.230149</v>
-      </c>
-      <c r="N70" s="2" t="n">
-        <v>69.206614</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>41.230149, 69.206614</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R70" t="n">
-        <v>302</v>
-      </c>
-      <c r="S70" t="n">
-        <v>8</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>да: 9 м</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V70"/>
+  <autoFilter ref="A1:V68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -4566,7 +4566,7 @@
         <v>379</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,7 @@
         <v>313</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 1613 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 6038 м</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -694,33 +694,29 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Бектемирский р-н, Бектемир Заргар cадово-виноградарное товарищество, 65</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкентская обл., нп. Ташкент, Новый Ташкентский р-н, Sihatgoh ko'chasi, 16</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ходжа 1</t>
+          <t>Ахмад Яссави</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41.210898</v>
+        <v>41.184703</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>69.295558</v>
+        <v>69.440258</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>41.210898, 69.295558</t>
+          <t>41.184703, 69.440258</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.210898,69.295558</t>
+          <t>https://www.google.com/maps?q=41.184703,69.440258</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -729,7 +725,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1613</v>
+        <v>6038</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -755,26 +751,26 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 618 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 1613 м</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ozon, Wildberries</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -784,54 +780,54 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Ташкент, улица Уста-Алима, 95</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Бектемирский р-н, Бектемир Заргар cадово-виноградарное товарищество, 65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Чилтуган махалля</t>
+          <t>Ходжа 1</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41.348045</v>
+        <v>41.210898</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>69.257784</v>
+        <v>69.295558</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>41.348045, 69.257784</t>
+          <t>41.210898, 69.295558</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.348045,69.257784</t>
+          <t>https://www.google.com/maps?q=41.210898,69.295558</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>618</v>
+        <v>1613</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -845,11 +841,11 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 514 м</t>
+          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 618 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -874,45 +870,45 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Ташкент, Мукими ул., 108</t>
+          <t>Ташкент, улица Уста-Алима, 95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Чиланзар махалля</t>
+          <t>Чилтуган махалля</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>41.288121</v>
+        <v>41.348045</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>69.230209</v>
+        <v>69.257784</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>41.288121, 69.230209</t>
+          <t>41.348045, 69.257784</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.288121,69.230209</t>
+          <t>https://www.google.com/maps?q=41.348045,69.257784</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>514</v>
+        <v>618</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -921,7 +917,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>да: 132 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,16 +931,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2 бренда (Ozon, Яндекс Маркет), 2 точки; ближайший Uzum в 450 м</t>
+          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 514 м</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ozon, Яндекс Маркет</t>
+          <t>Ozon, Wildberries</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -957,40 +953,40 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ташкент, Малая кольцевая дор., 77-1ф</t>
+          <t>Ташкент, Мукими ул., 108</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Чиланзар махалля</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41.348622</v>
+        <v>41.288121</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>69.234691</v>
+        <v>69.230209</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>41.348622, 69.234691</t>
+          <t>41.288121, 69.230209</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.348622,69.234691</t>
+          <t>https://www.google.com/maps?q=41.288121,69.230209</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -999,10 +995,10 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 132 м</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1025,16 +1021,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 396 м</t>
+          <t>2 бренда (Ozon, Яндекс Маркет), 2 точки; ближайший Uzum в 450 м</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ozon, Wildberries</t>
+          <t>Ozon, Яндекс Маркет</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1047,40 +1043,40 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ташкент, 14-й кв-л, 14А</t>
+          <t>Ташкент, Малая кольцевая дор., 77-1ф</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>41.37426</v>
+        <v>41.348622</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>69.301552</v>
+        <v>69.234691</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>41.374260, 69.301552</t>
+          <t>41.348622, 69.234691</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.374260,69.301552</t>
+          <t>https://www.google.com/maps?q=41.348622,69.234691</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1089,10 +1085,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1101,7 +1097,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>да: 236 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1115,16 +1111,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2 бренда (Wildberries, Яндекс Маркет), 2 точки; ближайший Uzum в 365 м; точки только из Яндекс Карт — проверить</t>
+          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 396 м</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wildberries, Яндекс Маркет</t>
+          <t>Ozon, Wildberries</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1134,55 +1130,55 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ташкент, Чиланзарский район, микрорайон Алмазар, 7</t>
+          <t>Ташкент, 14-й кв-л, 14А</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Алмазар массив</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41.310336</v>
+        <v>41.37426</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>69.24345099999999</v>
+        <v>69.301552</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>41.310336, 69.243451</t>
+          <t>41.374260, 69.301552</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.310336,69.243451</t>
+          <t>https://www.google.com/maps?q=41.374260,69.301552</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1191,7 +1187,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 236 м</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1209,7 +1205,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2 бренда (Wildberries, Яндекс Маркет), 2 точки; ближайший Uzum в 348 м</t>
+          <t>2 бренда (Wildberries, Яндекс Маркет), 2 точки; ближайший Uzum в 365 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1234,45 +1230,45 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 23-й кв-л, 17</t>
+          <t>Ташкент, Чиланзарский район, микрорайон Алмазар, 7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Чиланзар-23</t>
+          <t>Алмазар массив</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>41.285609</v>
+        <v>41.310336</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>69.176328</v>
+        <v>69.24345099999999</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>41.285609, 69.176328</t>
+          <t>41.310336, 69.243451</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285609,69.176328</t>
+          <t>https://www.google.com/maps?q=41.310336,69.243451</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1295,16 +1291,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 334 м</t>
+          <t>2 бренда (Wildberries, Яндекс Маркет), 2 точки; ближайший Uzum в 348 м</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ozon, Wildberries</t>
+          <t>Wildberries, Яндекс Маркет</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1314,43 +1310,43 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>массив Юнусабад, 13-й кв-л, 45</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 23-й кв-л, 17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Юнусабад 13-й квартал</t>
+          <t>Чиланзар-23</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41.367757</v>
+        <v>41.285609</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>69.302626</v>
+        <v>69.176328</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>41.367757, 69.302626</t>
+          <t>41.285609, 69.176328</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.367757,69.302626</t>
+          <t>https://www.google.com/maps?q=41.285609,69.176328</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1359,19 +1355,19 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1389,12 +1385,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 бренда (Wildberries, Яндекс Маркет), 2 точки; ближайший Uzum в 318 м</t>
+          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 334 м</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wildberries, Яндекс Маркет</t>
+          <t>Ozon, Wildberries</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1404,43 +1400,43 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ташкент, улица Авиасозлар 9</t>
+          <t>массив Юнусабад, 13-й кв-л, 45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Авиасозлар (Лисунова)</t>
+          <t>Юнусабад 13-й квартал</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41.289469</v>
+        <v>41.367757</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>69.34407400000001</v>
+        <v>69.302626</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>41.289469, 69.344074</t>
+          <t>41.367757, 69.302626</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.289469,69.344074</t>
+          <t>https://www.google.com/maps?q=41.367757,69.302626</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1449,19 +1445,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1475,16 +1471,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 315 м</t>
+          <t>2 бренда (Wildberries, Яндекс Маркет), 2 точки; ближайший Uzum в 318 м</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ozon, Wildberries</t>
+          <t>Wildberries, Яндекс Маркет</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1494,39 +1490,43 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>массив Куйлюк, 6-й кв-л, 5а</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>Ташкент, улица Авиасозлар 9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Куйлюк-6</t>
+          <t>Авиасозлар (Лисунова)</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>41.245046</v>
+        <v>41.289469</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>69.290358</v>
+        <v>69.34407400000001</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>41.245046, 69.290358</t>
+          <t>41.289469, 69.344074</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.245046,69.290358</t>
+          <t>https://www.google.com/maps?q=41.289469,69.344074</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>да: 94 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1561,26 +1561,26 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 801 м; точки только из Яндекс Карт — проверить</t>
+          <t>2 бренда (Ozon, Wildberries), 2 точки; ближайший Uzum в 315 м</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon, Wildberries</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1590,50 +1590,50 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Ташкент, Сергелийский район, махаллинский сход граждан Дарёбуйи</t>
+          <t>массив Куйлюк, 6-й кв-л, 5а</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Старые Сергели</t>
+          <t>Куйлюк-6</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>41.208913</v>
+        <v>41.245046</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>69.25659899999999</v>
+        <v>69.290358</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>41.208913, 69.256599</t>
+          <t>41.245046, 69.290358</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.208913,69.256599</t>
+          <t>https://www.google.com/maps?q=41.245046,69.290358</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>801</v>
+        <v>315</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 94 м</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1647,11 +1647,11 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 788 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 820 м</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкентская обл., нп. Ташкент, Новый Ташкентский р-н, Sihatgoh ko'chasi, 16</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Алишера Навои, 26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ахмад Яссави</t>
+          <t>Хадра (Ц-14)</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>41.184703</v>
+        <v>41.321559</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>69.440258</v>
+        <v>69.253536</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>41.184703, 69.440258</t>
+          <t>41.321559, 69.253536</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.184703,69.440258</t>
+          <t>https://www.google.com/maps?q=41.321559,69.253536</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>788</v>
+        <v>820</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 764 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 801 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1755,40 +1755,36 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Ташкентская область, Ташкент, улица Хусейна Байкары, 35B</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Сергелийский район, махаллинский сход граждан Дарёбуйи</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Старые Сергели</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>41.255216</v>
+        <v>41.208913</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>69.374576</v>
+        <v>69.25659899999999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>41.255216, 69.374576</t>
+          <t>41.208913, 69.256599</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.255216,69.374576</t>
+          <t>https://www.google.com/maps?q=41.208913,69.256599</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1797,19 +1793,19 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>764</v>
+        <v>801</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>да: 269 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1823,11 +1819,11 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 737 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 782 м</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1852,33 +1848,33 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 2-й пр-д Боситхон, 32</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Улуга Гулямова, 10А</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Урикзар</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>41.286849</v>
+        <v>41.405805</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>69.143169</v>
+        <v>69.45934200000001</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>41.286849, 69.143169</t>
+          <t>41.405805, 69.459342</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286849,69.143169</t>
+          <t>https://www.google.com/maps?q=41.405805,69.459342</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1887,19 +1883,19 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>737</v>
+        <v>782</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 259 м</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1913,16 +1909,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 732 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 764 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1935,57 +1931,61 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Кумарык, 32</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Ташкентская область, Ташкент, улица Хусейна Байкары, 35B</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Бектемирский район</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Кумарык махалля</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>41.249946</v>
+        <v>41.255216</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>69.25695899999999</v>
+        <v>69.374576</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>41.249946, 69.256959</t>
+          <t>41.255216, 69.374576</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.249946,69.256959</t>
+          <t>https://www.google.com/maps?q=41.255216,69.374576</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 269 м</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1999,11 +1999,11 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 712 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 751 м</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2028,33 +2028,29 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ташкент, массив Сувсоз-2 29</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтинводий, 11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Венгерская</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>41.254455</v>
+        <v>41.260607</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>69.376133</v>
+        <v>69.249556</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41.254455, 69.376133</t>
+          <t>41.260607, 69.249556</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254455,69.376133</t>
+          <t>https://www.google.com/maps?q=41.260607,69.249556</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2063,10 +2059,10 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>712</v>
+        <v>751</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2075,7 +2071,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>да: 224 м</t>
+          <t>да: 213 м</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2089,16 +2085,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 708 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 737 м</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2111,52 +2107,52 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 28</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 2-й пр-д Боситхон, 32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Вузгородок</t>
+          <t>Урикзар</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>41.346828</v>
+        <v>41.286849</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>69.205709</v>
+        <v>69.143169</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>41.346828, 69.205709</t>
+          <t>41.286849, 69.143169</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.346828,69.205709</t>
+          <t>https://www.google.com/maps?q=41.286849,69.143169</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2165,7 +2161,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>да: 66 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2179,11 +2175,11 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 699 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 732 м</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2208,29 +2204,29 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Алишера Навои, 26</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Кумарык, 32</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Хадра (Ц-14)</t>
+          <t>Кумарык махалля</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>41.321559</v>
+        <v>41.249946</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>69.253536</v>
+        <v>69.25695899999999</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>41.321559, 69.253536</t>
+          <t>41.249946, 69.256959</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.321559,69.253536</t>
+          <t>https://www.google.com/maps?q=41.249946,69.256959</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2239,10 +2235,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>699</v>
+        <v>732</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2265,11 +2261,11 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 664 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 712 м</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2294,29 +2290,33 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Чаштепа, 31</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Ташкент, массив Сувсоз-2 29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Бектемирский район</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ЖК "Домбрабад Тауерс"</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>41.248641</v>
+        <v>41.254455</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>69.210115</v>
+        <v>69.376133</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>41.248641, 69.210115</t>
+          <t>41.254455, 69.376133</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.248641,69.210115</t>
+          <t>https://www.google.com/maps?q=41.254455,69.376133</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>664</v>
+        <v>712</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 224 м</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2351,16 +2351,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 622 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 708 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2373,14 +2373,14 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Ташкент,   15</t>
+          <t>Ташкент, Ташкент, улица Фараби, 28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Чукурсай</t>
+          <t>Вузгородок</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>41.369273</v>
+        <v>41.346828</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>69.230796</v>
+        <v>69.205709</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>41.369273, 69.230796</t>
+          <t>41.346828, 69.205709</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.369273,69.230796</t>
+          <t>https://www.google.com/maps?q=41.346828,69.205709</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>622</v>
+        <v>708</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>да: 77 м</t>
+          <t>да: 66 м</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2441,16 +2441,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 620 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 668 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2463,61 +2463,61 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Катта Янгиабад, 7</t>
+          <t>Ташкент, Ташкент, улица Беруни, 15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Надыра махалля</t>
+          <t>Куёш махалля</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>41.27502</v>
+        <v>41.335977</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>69.350781</v>
+        <v>69.213432</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>41.275020, 69.350781</t>
+          <t>41.335977, 69.213432</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.275020,69.350781</t>
+          <t>https://www.google.com/maps?q=41.335977,69.213432</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 161 м</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2531,11 +2531,11 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 603 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 664 м</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2560,33 +2560,29 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 4-й пр-д Мингурик, 3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Юнусабадский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Чаштепа, 31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>ЖК "Домбрабад Тауерс"</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41.342982</v>
+        <v>41.248641</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>69.300478</v>
+        <v>69.210115</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>41.342982, 69.300478</t>
+          <t>41.248641, 69.210115</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.342982,69.300478</t>
+          <t>https://www.google.com/maps?q=41.248641,69.210115</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2595,19 +2591,19 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>603</v>
+        <v>664</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>да: 18 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2621,16 +2617,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 586 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 622 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2640,64 +2636,64 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ташкент, Иззат ул., 58/4</t>
+          <t>Ташкент,   15</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Чукурсай</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>41.272995</v>
+        <v>41.369273</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>69.340649</v>
+        <v>69.230796</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>41.272995, 69.340649</t>
+          <t>41.369273, 69.230796</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272995,69.340649</t>
+          <t>https://www.google.com/maps?q=41.369273,69.230796</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>586</v>
+        <v>622</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 77 м</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2711,16 +2707,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 477 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 620 м</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2730,43 +2726,43 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ташкент, Туркистан ул., 12</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Катта Янгиабад, 7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Надыра махалля</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>41.292276</v>
+        <v>41.27502</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>69.285268</v>
+        <v>69.350781</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>41.292276, 69.285268</t>
+          <t>41.275020, 69.350781</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.292276,69.285268</t>
+          <t>https://www.google.com/maps?q=41.275020,69.350781</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2775,19 +2771,19 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>477</v>
+        <v>620</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2801,16 +2797,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 603 м</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2823,61 +2819,61 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 4-й пр-д Мингурик, 3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>41.209344</v>
+        <v>41.342982</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>69.20008300000001</v>
+        <v>69.300478</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>41.209344, 69.200083</t>
+          <t>41.342982, 69.300478</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
+          <t>https://www.google.com/maps?q=41.342982,69.300478</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>443</v>
+        <v>603</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>да: 64 м</t>
+          <t>да: 18 м</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2891,16 +2887,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 601 м</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2913,52 +2909,52 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Дилкаш, 2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Шарк Юлдузи махалля</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>41.290617</v>
+        <v>41.313448</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>69.355688</v>
+        <v>69.180593</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>41.290617, 69.355688</t>
+          <t>41.313448, 69.180593</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
+          <t>https://www.google.com/maps?q=41.313448,69.180593</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>436</v>
+        <v>601</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2981,16 +2977,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 586 м</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3000,39 +2996,43 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>Ташкент, Иззат ул., 58/4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Зафарабад махалля</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41.34016</v>
+        <v>41.272995</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>69.199088</v>
+        <v>69.340649</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>41.340160, 69.199088</t>
+          <t>41.272995, 69.340649</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
+          <t>https://www.google.com/maps?q=41.272995,69.340649</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3041,19 +3041,19 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>434</v>
+        <v>586</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>да: 164 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3067,16 +3067,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 579 м</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3086,43 +3086,43 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+          <t>Ташкент, Туркистан ул., 12</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>41.295637</v>
+        <v>41.292276</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>69.331536</v>
+        <v>69.285268</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>41.295637, 69.331536</t>
+          <t>41.292276, 69.285268</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
+          <t>https://www.google.com/maps?q=41.292276,69.285268</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>434</v>
+        <v>579</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3157,16 +3157,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 537 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3179,49 +3179,49 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
+          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41.228417</v>
+        <v>41.272864</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>69.328615</v>
+        <v>69.24437</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>41.228417, 69.328615</t>
+          <t>41.272864, 69.244370</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
+          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>430</v>
+        <v>537</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 299 м</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3247,16 +3247,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 508 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3266,55 +3266,55 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ташкент,   51</t>
+          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ТТЗ-2</t>
+          <t>Чиланзар-18</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41.357678</v>
+        <v>41.274182</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>69.383498</v>
+        <v>69.190247</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.357678, 69.383498</t>
+          <t>41.274182, 69.190247</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
+          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>429</v>
+        <v>508</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3337,16 +3337,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3359,61 +3359,61 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
+          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Каракамыш 2/3</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41.370139</v>
+        <v>41.209344</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>69.215407</v>
+        <v>69.20008300000001</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>41.370139, 69.215407</t>
+          <t>41.209344, 69.200083</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
+          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 64 м</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3449,61 +3449,61 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
+          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41.279926</v>
+        <v>41.290617</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>69.181485</v>
+        <v>69.355688</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>41.279926, 69.181485</t>
+          <t>41.290617, 69.355688</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
+          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 435 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3539,48 +3539,52 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Ташкент, проспект Амира Темура, 51</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Мирабадский район</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Сергели-8</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41.221246</v>
+        <v>41.296327</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>69.222719</v>
+        <v>69.28720199999999</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>41.221246, 69.222719</t>
+          <t>41.296327, 69.287202</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
+          <t>https://www.google.com/maps?q=41.296327,69.287202</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3589,7 +3593,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 112 м</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3607,12 +3611,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -3625,61 +3629,57 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Юнусабадский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Зафарабад махалля</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41.3704</v>
+        <v>41.34016</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>69.303775</v>
+        <v>69.199088</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>41.370400, 69.303775</t>
+          <t>41.340160, 69.199088</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
+          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R36" t="n">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 164 м</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3722,33 +3722,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Бешагач махалля</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>41.304152</v>
+        <v>41.295637</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>69.24776199999999</v>
+        <v>69.331536</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>41.304152, 69.247762</t>
+          <t>41.295637, 69.331536</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
+          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3757,19 +3757,19 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3783,11 +3783,11 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3812,33 +3812,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>41.320524</v>
+        <v>41.228417</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>69.326745</v>
+        <v>69.328615</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>41.320524, 69.326745</t>
+          <t>41.228417, 69.328615</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
+          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>да: 87 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3873,11 +3873,11 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3902,33 +3902,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Ташкент,   3</t>
+          <t>Ташкент,   51</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>ТТЗ-2</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>41.285129</v>
+        <v>41.357678</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>69.21448700000001</v>
+        <v>69.383498</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>41.285129, 69.214487</t>
+          <t>41.357678, 69.383498</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
+          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3963,16 +3963,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 396 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -3985,49 +3985,49 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Каракамыш 2/3</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.272864</v>
+        <v>41.370139</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>69.24437</v>
+        <v>69.215407</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41.272864, 69.244370</t>
+          <t>41.370139, 69.215407</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
+          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>да: 299 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4053,11 +4053,11 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4092,23 +4092,23 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Чиланзар-25</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41.28283</v>
+        <v>41.279926</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>69.169132</v>
+        <v>69.181485</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>41.282830, 69.169132</t>
+          <t>41.279926, 69.181485</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
+          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4117,19 +4117,19 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="S41" t="n">
         <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4143,16 +4143,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4162,43 +4162,39 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Ташкент, Асака ул., 50-5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Мирзо Улугбекский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Сергели-8</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41.315832</v>
+        <v>41.221246</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>69.303838</v>
+        <v>69.222719</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>41.315832, 69.303838</t>
+          <t>41.221246, 69.222719</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
+          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4207,10 +4203,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>392</v>
+        <v>423</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4219,7 +4215,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>да: 86 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4233,16 +4229,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 419 м</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4255,52 +4251,52 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Абдурауфа Фитрата, 28</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Юнусабад-6</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>41.3711</v>
+        <v>41.271606</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>69.26542600000001</v>
+        <v>69.30528200000001</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.371100, 69.265426</t>
+          <t>41.271606, 69.305282</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
+          <t>https://www.google.com/maps?q=41.271606,69.305282</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4309,7 +4305,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 265 м</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4323,16 +4319,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 414 м</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4342,43 +4338,43 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
+          <t>Ташкент, Абдурауфа Фитрата ул., 13</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Алай (Ц-2)</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41.31665</v>
+        <v>41.271454</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>69.283869</v>
+        <v>69.30747700000001</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>41.316650, 69.283869</t>
+          <t>41.271454, 69.307477</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
+          <t>https://www.google.com/maps?q=41.271454,69.307477</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4387,10 +4383,10 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>385</v>
+        <v>414</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4413,16 +4409,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4435,61 +4431,61 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
+          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41.351161</v>
+        <v>41.3704</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>69.23766000000001</v>
+        <v>69.303775</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41.351161, 69.237660</t>
+          <t>41.370400, 69.303775</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
+          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>да: 13 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4503,11 +4499,11 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4532,29 +4528,33 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Чиланзарский район</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Абу Али ибн Сино-1</t>
+          <t>Бешагач махалля</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41.334773</v>
+        <v>41.304152</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>69.164872</v>
+        <v>69.24776199999999</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>41.334773, 69.164872</t>
+          <t>41.304152, 69.247762</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
+          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4563,19 +4563,19 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 1 м</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4618,33 +4618,33 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ташкент, 26-Й Квартал 30</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>41.274511</v>
+        <v>41.320524</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>69.174975</v>
+        <v>69.326745</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.274511, 69.174975</t>
+          <t>41.320524, 69.326745</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
+          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 87 м</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4679,11 +4679,11 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4708,33 +4708,33 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
+          <t>Ташкент,   3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Юнусабад-8</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41.368767</v>
+        <v>41.285129</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>69.27860200000001</v>
+        <v>69.21448700000001</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41.368767, 69.278602</t>
+          <t>41.285129, 69.214487</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
+          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>да: 120 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4769,16 +4769,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4788,17 +4788,17 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>массив Чиланзар, 14-й кв-л, 25</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4808,23 +4808,23 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>Чиланзар-25</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41.297736</v>
+        <v>41.28283</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>69.19082899999999</v>
+        <v>69.169132</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>41.297736, 69.190829</t>
+          <t>41.282830, 69.169132</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
+          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4859,16 +4859,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4878,43 +4878,43 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+          <t>Ташкент, Асака ул., 50-5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>41.344107</v>
+        <v>41.315832</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>69.209092</v>
+        <v>69.303838</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>41.344107, 69.209092</t>
+          <t>41.315832, 69.303838</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
+          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>да: 283 м</t>
+          <t>да: 86 м</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -4949,16 +4949,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4971,52 +4971,52 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
+          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Юнусабад-6</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>41.295273</v>
+        <v>41.3711</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>69.35441400000001</v>
+        <v>69.26542600000001</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>41.295273, 69.354414</t>
+          <t>41.371100, 69.265426</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
+          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5039,16 +5039,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 363 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5058,55 +5058,55 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Ташкент, улица Катта Олмос, 21</t>
+          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Алмаслык</t>
+          <t>Алай (Ц-2)</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41.271981</v>
+        <v>41.31665</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>69.368154</v>
+        <v>69.283869</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>41.271981, 69.368154</t>
+          <t>41.316650, 69.283869</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
+          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5129,11 +5129,11 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Ташкент Малая Кольцевая Дорога 19</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5168,23 +5168,23 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Чимбай махалля</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>41.3491</v>
+        <v>41.351161</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>69.216686</v>
+        <v>69.23766000000001</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>41.349100, 69.216686</t>
+          <t>41.351161, 69.237660</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
+          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>да: 13 м</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5219,16 +5219,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5241,56 +5241,52 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Яшнободский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Абу Али ибн Сино-1</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41.284162</v>
+        <v>41.334773</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>69.35999099999999</v>
+        <v>69.164872</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>41.284162, 69.359991</t>
+          <t>41.334773, 69.164872</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
+          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -5309,11 +5305,11 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5338,33 +5334,33 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
+          <t>Ташкент, 26-Й Квартал 30</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Чиланзар-16</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41.272128</v>
+        <v>41.274511</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>69.200819</v>
+        <v>69.174975</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>41.272128, 69.200819</t>
+          <t>41.274511, 69.174975</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
+          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5373,10 +5369,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5399,16 +5395,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -5418,55 +5414,55 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Ташкент, 2-й квартал, 18</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Тузель-2</t>
+          <t>Юнусабад-8</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41.291661</v>
+        <v>41.368767</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>69.36116</v>
+        <v>69.27860200000001</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>41.291661, 69.361160</t>
+          <t>41.368767, 69.278602</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
+          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5475,7 +5471,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 120 м</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5489,16 +5485,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5508,55 +5504,55 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
+          <t>массив Чиланзар, 14-й кв-л, 25</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа махалля</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>41.349977</v>
+        <v>41.297736</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>69.190336</v>
+        <v>69.19082899999999</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>41.349977, 69.190336</t>
+          <t>41.297736, 69.190829</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
+          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5579,16 +5575,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 368 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -5598,55 +5594,55 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
+          <t>Ташкент, улица Катта Олмос, 21</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Минор (Ц-6)</t>
+          <t>Алмаслык</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>41.337068</v>
+        <v>41.271981</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>69.285428</v>
+        <v>69.368154</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>41.337068, 69.285428</t>
+          <t>41.271981, 69.368154</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
+          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5655,7 +5651,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>да: 46 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5669,11 +5665,11 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5698,33 +5694,33 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41.314418</v>
+        <v>41.344107</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>69.32381700000001</v>
+        <v>69.209092</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>41.314418, 69.323817</t>
+          <t>41.344107, 69.209092</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5733,7 +5729,7 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -5745,7 +5741,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 283 м</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5759,11 +5755,11 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5788,33 +5784,33 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Геофизика</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41.338894</v>
+        <v>41.295273</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>69.386939</v>
+        <v>69.35441400000001</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>41.338894, 69.386939</t>
+          <t>41.295273, 69.354414</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5823,10 +5819,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5849,16 +5845,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -5871,52 +5867,52 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+          <t>Ташкент Малая Кольцевая Дорога 19</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Сергели</t>
+          <t>Чимбай махалля</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41.214477</v>
+        <v>41.3491</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>69.212414</v>
+        <v>69.216686</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>41.214477, 69.212414</t>
+          <t>41.349100, 69.216686</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>323</v>
+        <v>362</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5925,7 +5921,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -5939,16 +5935,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -5961,14 +5957,14 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5978,35 +5974,35 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>41.24192</v>
+        <v>41.284162</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>69.33096</v>
+        <v>69.35999099999999</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>41.241920, 69.330960</t>
+          <t>41.284162, 69.359991</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6029,16 +6025,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6048,43 +6044,43 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Ташкент, массив Аханграбо, 8</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Чиланзар-16</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41.252678</v>
+        <v>41.272128</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>69.344067</v>
+        <v>69.200819</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>41.252678, 69.344067</t>
+          <t>41.272128, 69.200819</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6093,10 +6089,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6105,7 +6101,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>да: 104 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6119,11 +6115,11 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6148,33 +6144,33 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
+          <t>Ташкент, 2-й квартал, 18</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Чиланзар-18</t>
+          <t>Тузель-2</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>41.274182</v>
+        <v>41.291661</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>69.190247</v>
+        <v>69.36116</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>41.274182, 69.190247</t>
+          <t>41.291661, 69.361160</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
+          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6183,10 +6179,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6209,16 +6205,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6231,52 +6227,52 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ташкент, 8-Й Квартал 1</t>
+          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Чиланзар-6</t>
+          <t>Чигатай-Актепа махалля</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41.287081</v>
+        <v>41.349977</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>69.205814</v>
+        <v>69.190336</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>41.287081, 69.205814</t>
+          <t>41.349977, 69.190336</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6299,11 +6295,11 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6328,33 +6324,33 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ташкент, улица Буюк Ипак Йули 77</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41.326369</v>
+        <v>41.337068</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>69.32475700000001</v>
+        <v>69.285428</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>41.326369, 69.324757</t>
+          <t>41.337068, 69.285428</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6363,10 +6359,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6375,7 +6371,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 46 м</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6389,11 +6385,11 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 336 м</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6418,33 +6414,33 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
+          <t>Ташкент, улица Бабура 67/1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41.235793</v>
+        <v>41.280974</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>69.352153</v>
+        <v>69.258222</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>41.235793, 69.352153</t>
+          <t>41.280974, 69.258222</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
+          <t>https://www.google.com/maps?q=41.280974,69.258222</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6453,10 +6449,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6465,7 +6461,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>да: 295 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6479,89 +6475,989 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
+        <v>21</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Риёзи (Чизельный)</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>41.314418</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>69.32381700000001</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>41.314418, 69.323817</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>335</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>21</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Мирзо Улугбекский район</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Геофизика</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>41.338894</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>69.386939</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>41.338894, 69.386939</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>330</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>21</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Яндекс Маркет</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Янгихаётский район</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Сергели</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>41.214477</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>69.212414</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>41.214477, 69.212414</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>323</v>
+      </c>
+      <c r="S70" t="n">
+        <v>8</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>21</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 322 м</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 19-й кв-л, 31</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Чиланзарский район</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Чиланзар-19</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>41.269818</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>69.184703</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>41.269818, 69.184703</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.269818,69.184703</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>322</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>21</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Куйлюк Центр</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>41.24192</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>69.33096</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>41.241920, 69.330960</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>321</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
         <v>20</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Ташкент, массив Аханграбо, 8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Аханграбо (Панельный)</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>41.252678</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>69.344067</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>41.252678, 69.344067</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>315</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>да: 104 м</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>20</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 309 м</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 3-й кв-л, 53</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Чиланзарский район</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Чиланзар-3</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>41.283594</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>69.22244600000001</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>41.283594, 69.222446</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.283594,69.222446</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>309</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>20</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Ташкент, 8-Й Квартал 1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Чиланзарский район</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Чиланзар-6</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>41.287081</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>69.205814</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>41.287081, 69.205814</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>308</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>20</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Ташкент, улица Буюк Ипак Йули 77</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Мирзо Улугбекский район</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Буюк Ипак Йули махалля</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>41.326369</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>69.32475700000001</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>41.326369, 69.324757</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>307</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>20</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Wildberries</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Бектемирский район</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Бузаучи</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>41.235793</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>69.352153</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>41.235793, 69.352153</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>306</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>запретная</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>да: 295 м</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>20</v>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Яндекс Маркет</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Сергели-6А</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n">
+      <c r="M78" s="2" t="n">
         <v>41.230149</v>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N78" s="2" t="n">
         <v>69.206614</v>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>41.230149, 69.206614</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=41.230149,69.206614</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="R68" t="n">
+      <c r="R78" t="n">
         <v>302</v>
       </c>
-      <c r="S68" t="n">
-        <v>8</v>
-      </c>
-      <c r="T68" t="inlineStr">
+      <c r="S78" t="n">
+        <v>7</v>
+      </c>
+      <c r="T78" t="inlineStr">
         <is>
           <t>запретная</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>да: 9 м</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V68"/>
+  <autoFilter ref="A1:V78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -642,7 +642,7 @@
         <v>313</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>365</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>318</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3247,16 +3247,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 508 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3266,43 +3266,43 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
+          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Чиланзар-18</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41.274182</v>
+        <v>41.209344</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>69.190247</v>
+        <v>69.20008300000001</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.274182, 69.190247</t>
+          <t>41.209344, 69.200083</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
+          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3311,19 +3311,19 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>508</v>
+        <v>443</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 64 м</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3366,33 +3366,33 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
+          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41.209344</v>
+        <v>41.290617</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>69.20008300000001</v>
+        <v>69.355688</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>41.209344, 69.200083</t>
+          <t>41.290617, 69.355688</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
+          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3401,19 +3401,19 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>да: 64 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3427,11 +3427,11 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 435 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3456,33 +3456,33 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
+          <t>Ташкент, проспект Амира Темура, 51</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41.290617</v>
+        <v>41.296327</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>69.355688</v>
+        <v>69.28720199999999</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>41.290617, 69.355688</t>
+          <t>41.296327, 69.287202</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
+          <t>https://www.google.com/maps?q=41.296327,69.287202</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 112 м</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 435 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3539,61 +3539,57 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Ташкент, проспект Амира Темура, 51</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Мирабадский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Зафарабад махалля</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41.296327</v>
+        <v>41.34016</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>69.28720199999999</v>
+        <v>69.199088</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>41.296327, 69.287202</t>
+          <t>41.340160, 69.199088</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.296327,69.287202</t>
+          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>да: 112 м</t>
+          <t>да: 164 м</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3636,29 +3632,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Зафарабад махалля</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41.34016</v>
+        <v>41.295637</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>69.199088</v>
+        <v>69.331536</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>41.340160, 69.199088</t>
+          <t>41.295637, 69.331536</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
+          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3670,16 +3670,16 @@
         <v>434</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>да: 164 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3722,33 +3722,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>41.295637</v>
+        <v>41.228417</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>69.331536</v>
+        <v>69.328615</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>41.295637, 69.331536</t>
+          <t>41.228417, 69.328615</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
+          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3757,19 +3757,19 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3812,33 +3812,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
+          <t>Ташкент,   51</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>ТТЗ-2</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>41.228417</v>
+        <v>41.357678</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>69.328615</v>
+        <v>69.383498</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>41.228417, 69.328615</t>
+          <t>41.357678, 69.383498</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
+          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3902,33 +3902,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Ташкент,   51</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ТТЗ-2</t>
+          <t>Каракамыш 2/3</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>41.357678</v>
+        <v>41.370139</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>69.383498</v>
+        <v>69.215407</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>41.357678, 69.383498</t>
+          <t>41.370139, 69.215407</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
+          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3992,33 +3992,33 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Каракамыш 2/3</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.370139</v>
+        <v>41.279926</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>69.215407</v>
+        <v>69.181485</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41.370139, 69.215407</t>
+          <t>41.279926, 69.181485</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
+          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4027,19 +4027,19 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4082,33 +4082,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Учтепинский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Сергели-8</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41.279926</v>
+        <v>41.221246</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>69.181485</v>
+        <v>69.222719</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>41.279926, 69.181485</t>
+          <t>41.221246, 69.222719</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
+          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4117,19 +4113,19 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4147,7 +4143,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 419 м</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4172,29 +4168,33 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Абдурауфа Фитрата, 28</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Мирабадский район</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Сергели-8</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41.221246</v>
+        <v>41.271606</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>69.222719</v>
+        <v>69.30528200000001</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>41.221246, 69.222719</t>
+          <t>41.271606, 69.305282</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
+          <t>https://www.google.com/maps?q=41.271606,69.305282</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 123 м</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 419 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 414 м</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4248,17 +4248,17 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Абдурауфа Фитрата, 28</t>
+          <t>Ташкент, Абдурауфа Фитрата ул., 13</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4272,19 +4272,19 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>41.271606</v>
+        <v>41.271454</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>69.30528200000001</v>
+        <v>69.30747700000001</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.271606, 69.305282</t>
+          <t>41.271454, 69.307477</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271606,69.305282</t>
+          <t>https://www.google.com/maps?q=41.271454,69.307477</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>да: 265 м</t>
+          <t>да: 23 м</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 414 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4338,64 +4338,64 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ташкент, Абдурауфа Фитрата ул., 13</t>
+          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41.271454</v>
+        <v>41.3704</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>69.30747700000001</v>
+        <v>69.303775</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>41.271454, 69.307477</t>
+          <t>41.370400, 69.303775</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271454,69.307477</t>
+          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R44" t="n">
         <v>414</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4431,61 +4431,61 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Бешагач махалля</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41.3704</v>
+        <v>41.304152</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>69.303775</v>
+        <v>69.24776199999999</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41.370400, 69.303775</t>
+          <t>41.304152, 69.247762</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
+          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 1 м</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4499,11 +4499,11 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4528,33 +4528,33 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Бешагач махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41.304152</v>
+        <v>41.320524</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>69.24776199999999</v>
+        <v>69.326745</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>41.304152, 69.247762</t>
+          <t>41.320524, 69.326745</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
+          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>да: 87 м</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4618,33 +4618,33 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
+          <t>Ташкент,   3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>41.320524</v>
+        <v>41.285129</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>69.326745</v>
+        <v>69.21448700000001</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.320524, 69.326745</t>
+          <t>41.285129, 69.214487</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
+          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>да: 87 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4708,33 +4708,33 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ташкент,   3</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Чиланзар-25</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41.285129</v>
+        <v>41.28283</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>69.21448700000001</v>
+        <v>69.169132</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41.285129, 69.214487</t>
+          <t>41.282830, 69.169132</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
+          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4788,43 +4788,43 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
+          <t>Ташкент, Асака ул., 50-5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Чиланзар-25</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41.28283</v>
+        <v>41.315832</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>69.169132</v>
+        <v>69.303838</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>41.282830, 69.169132</t>
+          <t>41.315832, 69.303838</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
+          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 86 м</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4878,55 +4878,55 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ташкент, Асака ул., 50-5</t>
+          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Юнусабад-6</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>41.315832</v>
+        <v>41.3711</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>69.303838</v>
+        <v>69.26542600000001</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>41.315832, 69.303838</t>
+          <t>41.371100, 69.265426</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
+          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>да: 86 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -4971,14 +4971,14 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
+          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4988,35 +4988,35 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Юнусабад-6</t>
+          <t>Алай (Ц-2)</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>41.3711</v>
+        <v>41.31665</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>69.26542600000001</v>
+        <v>69.283869</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>41.371100, 69.265426</t>
+          <t>41.316650, 69.283869</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
+          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5068,33 +5068,33 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Алай (Ц-2)</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41.31665</v>
+        <v>41.351161</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>69.283869</v>
+        <v>69.23766000000001</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>41.316650, 69.283869</t>
+          <t>41.351161, 69.237660</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
+          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 13 м</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5158,33 +5158,29 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Абу Али ибн Сино-1</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>41.351161</v>
+        <v>41.334773</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>69.23766000000001</v>
+        <v>69.164872</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>41.351161, 69.237660</t>
+          <t>41.334773, 69.164872</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
+          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5193,19 +5189,19 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>да: 13 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5223,7 +5219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5248,29 +5244,33 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>Ташкент, 26-Й Квартал 30</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Абу Али ибн Сино-1</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41.334773</v>
+        <v>41.274511</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>69.164872</v>
+        <v>69.174975</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>41.334773, 69.164872</t>
+          <t>41.274511, 69.174975</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
+          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5279,14 +5279,14 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -5305,11 +5305,11 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Ташкент, 26-Й Квартал 30</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Юнусабад-8</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41.274511</v>
+        <v>41.368767</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>69.174975</v>
+        <v>69.27860200000001</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>41.274511, 69.174975</t>
+          <t>41.368767, 69.278602</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
+          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 120 м</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -5414,43 +5414,43 @@
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
+          <t>массив Чиланзар, 14-й кв-л, 25</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Юнусабад-8</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41.368767</v>
+        <v>41.297736</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>69.27860200000001</v>
+        <v>69.19082899999999</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>41.368767, 69.278602</t>
+          <t>41.297736, 69.190829</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
+          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>да: 120 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 368 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5514,45 +5514,45 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>массив Чиланзар, 14-й кв-л, 25</t>
+          <t>Ташкент, улица Катта Олмос, 21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>Алмаслык</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>41.297736</v>
+        <v>41.271981</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>69.19082899999999</v>
+        <v>69.368154</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>41.297736, 69.190829</t>
+          <t>41.271981, 69.368154</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
+          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 368 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -5594,55 +5594,55 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Ташкент, улица Катта Олмос, 21</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Алмаслык</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>41.271981</v>
+        <v>41.344107</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>69.368154</v>
+        <v>69.209092</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>41.271981, 69.368154</t>
+          <t>41.344107, 69.209092</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
+          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 283 м</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5694,33 +5694,33 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41.344107</v>
+        <v>41.295273</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>69.209092</v>
+        <v>69.35441400000001</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>41.344107, 69.209092</t>
+          <t>41.295273, 69.354414</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
+          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>да: 283 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5784,33 +5784,33 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
+          <t>Ташкент Малая Кольцевая Дорога 19</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Чимбай махалля</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41.295273</v>
+        <v>41.3491</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>69.35441400000001</v>
+        <v>69.216686</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>41.295273, 69.354414</t>
+          <t>41.349100, 69.216686</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
+          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -5867,52 +5867,52 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ташкент Малая Кольцевая Дорога 19</t>
+          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Чимбай махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41.3491</v>
+        <v>41.284162</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>69.216686</v>
+        <v>69.35999099999999</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>41.349100, 69.216686</t>
+          <t>41.284162, 69.359991</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
+          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -5957,52 +5957,52 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Чиланзар-16</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>41.284162</v>
+        <v>41.272128</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>69.35999099999999</v>
+        <v>69.200819</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>41.284162, 69.359991</t>
+          <t>41.272128, 69.200819</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
+          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6044,55 +6044,55 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
+          <t>Ташкент, 2-й квартал, 18</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Чиланзар-16</t>
+          <t>Тузель-2</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41.272128</v>
+        <v>41.291661</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>69.200819</v>
+        <v>69.36116</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>41.272128, 69.200819</t>
+          <t>41.291661, 69.361160</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
+          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6134,43 +6134,43 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Ташкент, 2-й квартал, 18</t>
+          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Тузель-2</t>
+          <t>Чигатай-Актепа махалля</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>41.291661</v>
+        <v>41.349977</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>69.36116</v>
+        <v>69.190336</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>41.291661, 69.361160</t>
+          <t>41.349977, 69.190336</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
+          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа махалля</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41.349977</v>
+        <v>41.337068</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>69.190336</v>
+        <v>69.285428</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>41.349977, 69.190336</t>
+          <t>41.337068, 69.285428</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
+          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 46 м</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 336 м</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6324,33 +6324,33 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
+          <t>Ташкент, улица Бабура 67/1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Минор (Ц-6)</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41.337068</v>
+        <v>41.280974</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>69.285428</v>
+        <v>69.258222</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>41.337068, 69.285428</t>
+          <t>41.280974, 69.258222</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
+          <t>https://www.google.com/maps?q=41.280974,69.258222</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>да: 46 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 336 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6414,33 +6414,33 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Ташкент, улица Бабура 67/1</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Риёзи (Чизельный)</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41.280974</v>
+        <v>41.314418</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>69.258222</v>
+        <v>69.32381700000001</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>41.280974, 69.258222</t>
+          <t>41.314418, 69.323817</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.280974,69.258222</t>
+          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6504,33 +6504,33 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>Геофизика</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>41.314418</v>
+        <v>41.338894</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>69.32381700000001</v>
+        <v>69.386939</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>41.314418, 69.323817</t>
+          <t>41.338894, 69.386939</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -6587,52 +6587,52 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Геофизика</t>
+          <t>Сергели</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>41.338894</v>
+        <v>41.214477</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>69.386939</v>
+        <v>69.212414</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>41.338894, 69.386939</t>
+          <t>41.214477, 69.212414</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6659,12 +6659,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 322 м</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -6677,52 +6677,52 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 19-й кв-л, 31</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Сергели</t>
+          <t>Чиланзар-19</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>41.214477</v>
+        <v>41.269818</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>69.212414</v>
+        <v>69.184703</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>41.214477, 69.212414</t>
+          <t>41.269818, 69.184703</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+          <t>https://www.google.com/maps?q=41.269818,69.184703</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R70" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 322 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6774,33 +6774,33 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 19-й кв-л, 31</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Чиланзар-19</t>
+          <t>Куйлюк Центр</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>41.269818</v>
+        <v>41.24192</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>69.184703</v>
+        <v>69.33096</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>41.269818, 69.184703</t>
+          <t>41.241920, 69.330960</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.269818,69.184703</t>
+          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 175 м</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -6854,17 +6854,17 @@
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+          <t>Ташкент, массив Аханграбо, 8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6874,23 +6874,23 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>41.24192</v>
+        <v>41.252678</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>69.33096</v>
+        <v>69.344067</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>41.241920, 69.330960</t>
+          <t>41.252678, 69.344067</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6954,45 +6954,45 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Ташкент, массив Аханграбо, 8</t>
+          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Чиланзар-18</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41.252678</v>
+        <v>41.274182</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>69.344067</v>
+        <v>69.190247</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>41.252678, 69.344067</t>
+          <t>41.274182, 69.190247</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="S73" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>да: 104 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>да: 295 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7438,7 +7438,7 @@
         <v>302</v>
       </c>
       <c r="S78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V78"/>
+  <dimension ref="A1:V77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 155 м</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -998,7 +998,7 @@
         <v>514</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>да: 259 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>да: 213 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 668 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 664 м</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2463,61 +2463,57 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Беруни, 15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Чаштепа, 31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Куёш махалля</t>
+          <t>ЖК "Домбрабад Тауерс"</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>41.335977</v>
+        <v>41.248641</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>69.213432</v>
+        <v>69.210115</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>41.335977, 69.213432</t>
+          <t>41.248641, 69.210115</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.335977,69.213432</t>
+          <t>https://www.google.com/maps?q=41.248641,69.210115</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>да: 161 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2531,11 +2527,11 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 664 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 622 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2560,41 +2556,45 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Чаштепа, 31</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Ташкент,   15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Алмазарский район</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ЖК "Домбрабад Тауерс"</t>
+          <t>Чукурсай</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41.248641</v>
+        <v>41.369273</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>69.210115</v>
+        <v>69.230796</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>41.248641, 69.210115</t>
+          <t>41.369273, 69.230796</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.248641,69.210115</t>
+          <t>https://www.google.com/maps?q=41.369273,69.230796</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>664</v>
+        <v>622</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>да: 77 м</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 622 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 620 м</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2646,42 +2646,42 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ташкент,   15</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Катта Янгиабад, 7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Чукурсай</t>
+          <t>Надыра махалля</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>41.369273</v>
+        <v>41.27502</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>69.230796</v>
+        <v>69.350781</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>41.369273, 69.230796</t>
+          <t>41.275020, 69.350781</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.369273,69.230796</t>
+          <t>https://www.google.com/maps?q=41.275020,69.350781</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>да: 77 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2707,11 +2707,11 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 620 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 603 м</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2736,33 +2736,33 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Катта Янгиабад, 7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 4-й пр-д Мингурик, 3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Надыра махалля</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>41.27502</v>
+        <v>41.342982</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>69.350781</v>
+        <v>69.300478</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>41.275020, 69.350781</t>
+          <t>41.342982, 69.300478</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.275020,69.350781</t>
+          <t>https://www.google.com/maps?q=41.342982,69.300478</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 18 м</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 603 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 601 м</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2826,33 +2826,33 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 4-й пр-д Мингурик, 3</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Дилкаш, 2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>Шарк Юлдузи махалля</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>41.342982</v>
+        <v>41.313448</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>69.300478</v>
+        <v>69.180593</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>41.342982, 69.300478</t>
+          <t>41.313448, 69.180593</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.342982,69.300478</t>
+          <t>https://www.google.com/maps?q=41.313448,69.180593</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>да: 18 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 601 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 586 м</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2906,43 +2906,43 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Дилкаш, 2</t>
+          <t>Ташкент, Иззат ул., 58/4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Шарк Юлдузи махалля</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>41.313448</v>
+        <v>41.272995</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>69.180593</v>
+        <v>69.340649</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>41.313448, 69.180593</t>
+          <t>41.272995, 69.340649</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.313448,69.180593</t>
+          <t>https://www.google.com/maps?q=41.272995,69.340649</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2977,11 +2977,11 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 586 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 579 м</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3006,33 +3006,33 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Ташкент, Иззат ул., 58/4</t>
+          <t>Ташкент, Туркистан ул., 12</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>41.272995</v>
+        <v>41.292276</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>69.340649</v>
+        <v>69.285268</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>41.272995, 69.340649</t>
+          <t>41.292276, 69.285268</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272995,69.340649</t>
+          <t>https://www.google.com/maps?q=41.292276,69.285268</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3041,19 +3041,19 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 78 м</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3067,16 +3067,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 579 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 537 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3086,64 +3086,64 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Ташкент, Туркистан ул., 12</t>
+          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>41.292276</v>
+        <v>41.272864</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>69.285268</v>
+        <v>69.24437</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>41.292276, 69.285268</t>
+          <t>41.272864, 69.244370</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.292276,69.285268</t>
+          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>579</v>
+        <v>537</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 299 м</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3157,11 +3157,11 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 537 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3186,33 +3186,33 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Ташкентская область, Ташкент, улица Кушбеги, 14</t>
+          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>41.272864</v>
+        <v>41.209344</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>69.24437</v>
+        <v>69.20008300000001</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>41.272864, 69.244370</t>
+          <t>41.209344, 69.200083</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272864,69.244370</t>
+          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3221,19 +3221,19 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>537</v>
+        <v>443</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>да: 299 м</t>
+          <t>да: 64 м</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 443 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3276,33 +3276,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ташкентская область, Янгихаётский район, Ташкент, квартал Г64, 123</t>
+          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>41.209344</v>
+        <v>41.290617</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>69.20008300000001</v>
+        <v>69.355688</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.209344, 69.200083</t>
+          <t>41.290617, 69.355688</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.209344,69.200083</t>
+          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3311,19 +3311,19 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>да: 64 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3337,11 +3337,11 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 436 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 435 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3366,33 +3366,33 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ташкентская область, Яшнободский район, Ташкент, массив Городок Авиастроителей, 1-й квартал, 1</t>
+          <t>Ташкент, проспект Амира Темура, 51</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>41.290617</v>
+        <v>41.296327</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>69.355688</v>
+        <v>69.28720199999999</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>41.290617, 69.355688</t>
+          <t>41.296327, 69.287202</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.290617,69.355688</t>
+          <t>https://www.google.com/maps?q=41.296327,69.287202</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 277 м</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 435 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3449,61 +3449,57 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Ташкент, проспект Амира Темура, 51</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Мирабадский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Зафарабад махалля</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>41.296327</v>
+        <v>41.34016</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>69.28720199999999</v>
+        <v>69.199088</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>41.296327, 69.287202</t>
+          <t>41.340160, 69.199088</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.296327,69.287202</t>
+          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>да: 112 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3546,29 +3542,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, ул. Жаханаро, 1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Яшнободский район</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Зафарабад махалля</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41.34016</v>
+        <v>41.295637</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>69.199088</v>
+        <v>69.331536</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>41.340160, 69.199088</t>
+          <t>41.295637, 69.331536</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.340160,69.199088</t>
+          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3580,16 +3580,16 @@
         <v>434</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>да: 164 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 434 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3632,33 +3632,33 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Эльбека, 26</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>41.295637</v>
+        <v>41.228417</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>69.331536</v>
+        <v>69.328615</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>41.295637, 69.331536</t>
+          <t>41.228417, 69.328615</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295637,69.331536</t>
+          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 430 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3722,33 +3722,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Олтин Топган, 10</t>
+          <t>Ташкент,   51</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>ТТЗ-2</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>41.228417</v>
+        <v>41.357678</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>69.328615</v>
+        <v>69.383498</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>41.228417, 69.328615</t>
+          <t>41.357678, 69.383498</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228417,69.328615</t>
+          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3812,33 +3812,33 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Ташкент,   51</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ТТЗ-2</t>
+          <t>Каракамыш 2/3</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>41.357678</v>
+        <v>41.370139</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>69.383498</v>
+        <v>69.215407</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>41.357678, 69.383498</t>
+          <t>41.370139, 69.215407</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.357678,69.383498</t>
+          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 429 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3902,33 +3902,33 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, 1-я ул. Каракамыш, 11</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Каракамыш 2/3</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>41.370139</v>
+        <v>41.279926</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>69.215407</v>
+        <v>69.181485</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>41.370139, 69.215407</t>
+          <t>41.279926, 69.181485</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370139,69.215407</t>
+          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3937,19 +3937,19 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 426 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3992,33 +3992,29 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 26-й кв-л, 2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Учтепинский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Сергели-8</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>41.279926</v>
+        <v>41.221246</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>69.181485</v>
+        <v>69.222719</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>41.279926, 69.181485</t>
+          <t>41.221246, 69.222719</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.279926,69.181485</t>
+          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4027,19 +4023,19 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4057,7 +4053,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 423 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 419 м</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4082,29 +4078,33 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Сергелийский р-н, ул. Янги Сергели, 21А</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Абдурауфа Фитрата, 28</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Мирабадский район</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Сергели-8</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>41.221246</v>
+        <v>41.271606</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>69.222719</v>
+        <v>69.30528200000001</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>41.221246, 69.222719</t>
+          <t>41.271606, 69.305282</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221246,69.222719</t>
+          <t>https://www.google.com/maps?q=41.271606,69.305282</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 265 м</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 419 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 414 м</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4158,17 +4158,17 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Абдурауфа Фитрата, 28</t>
+          <t>Ташкент, Абдурауфа Фитрата ул., 13</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4182,19 +4182,19 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41.271606</v>
+        <v>41.271454</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>69.30528200000001</v>
+        <v>69.30747700000001</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>41.271606, 69.305282</t>
+          <t>41.271454, 69.307477</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271606,69.305282</t>
+          <t>https://www.google.com/maps?q=41.271454,69.307477</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>да: 123 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 414 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4248,64 +4248,64 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ташкент, Абдурауфа Фитрата ул., 13</t>
+          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Юнусабад-14</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>41.271454</v>
+        <v>41.3704</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>69.30747700000001</v>
+        <v>69.303775</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>41.271454, 69.307477</t>
+          <t>41.370400, 69.303775</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271454,69.307477</t>
+          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R43" t="n">
         <v>414</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>да: 23 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 414 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4341,61 +4341,61 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 14-й квартал, 67</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Юнусабад-14</t>
+          <t>Бешагач махалля</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41.3704</v>
+        <v>41.304152</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>69.303775</v>
+        <v>69.24776199999999</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>41.370400, 69.303775</t>
+          <t>41.304152, 69.247762</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370400,69.303775</t>
+          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 1 м</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4409,11 +4409,11 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 412 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4438,33 +4438,33 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фурката, 167</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Бешагач махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>41.304152</v>
+        <v>41.320524</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>69.24776199999999</v>
+        <v>69.326745</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>41.304152, 69.247762</t>
+          <t>41.320524, 69.326745</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.304152,69.247762</t>
+          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>да: 87 м</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 404 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4528,33 +4528,33 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Мухаммада Юсуфа, 41</t>
+          <t>Ташкент,   3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>41.320524</v>
+        <v>41.285129</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>69.326745</v>
+        <v>69.21448700000001</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>41.320524, 69.326745</t>
+          <t>41.285129, 69.214487</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.320524,69.326745</t>
+          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="S46" t="n">
         <v>8</v>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>да: 87 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 400 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4618,33 +4618,33 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Ташкент,   3</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Чиланзар-25</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>41.285129</v>
+        <v>41.28283</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>69.21448700000001</v>
+        <v>69.169132</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.285129, 69.214487</t>
+          <t>41.282830, 69.169132</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285129,69.214487</t>
+          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 393 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4698,43 +4698,43 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Учтепинский р-н, 25-й кв-л, 2</t>
+          <t>Ташкент, Асака ул., 50-5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Чиланзар-25</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41.28283</v>
+        <v>41.315832</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>69.169132</v>
+        <v>69.303838</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41.282830, 69.169132</t>
+          <t>41.315832, 69.303838</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282830,69.169132</t>
+          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 86 м</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 392 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4788,55 +4788,55 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Ташкент, Асака ул., 50-5</t>
+          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Юнусабад-6</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41.315832</v>
+        <v>41.3711</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>69.303838</v>
+        <v>69.26542600000001</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>41.315832, 69.303838</t>
+          <t>41.371100, 69.265426</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315832,69.303838</t>
+          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>да: 86 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 387 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -4881,14 +4881,14 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, 7-й квартал, 49</t>
+          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4898,35 +4898,35 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Юнусабад-6</t>
+          <t>Алай (Ц-2)</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>41.3711</v>
+        <v>41.31665</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>69.26542600000001</v>
+        <v>69.283869</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>41.371100, 69.265426</t>
+          <t>41.316650, 69.283869</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.371100,69.265426</t>
+          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 385 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4978,33 +4978,33 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>г. Ташкент, Ул. Шахрисабз д.7</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Алай (Ц-2)</t>
+          <t>Каракамыш 1/1</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>41.31665</v>
+        <v>41.351161</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>69.283869</v>
+        <v>69.23766000000001</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>41.316650, 69.283869</t>
+          <t>41.351161, 69.237660</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316650,69.283869</t>
+          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 13 м</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 380 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5068,33 +5068,29 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Алмазарский р-н, кв-л 1/1, 23</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Алмазарский район</t>
-        </is>
-      </c>
+          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Каракамыш 1/1</t>
+          <t>Абу Али ибн Сино-1</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41.351161</v>
+        <v>41.334773</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>69.23766000000001</v>
+        <v>69.164872</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>41.351161, 69.237660</t>
+          <t>41.334773, 69.164872</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351161,69.237660</t>
+          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5103,19 +5099,19 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>да: 13 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5133,7 +5129,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 379 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5158,29 +5154,33 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Шайхантахурский р-н, массив Ибн Сина-1, 7</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>Ташкент, 26-Й Квартал 30</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Учтепинский район</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Абу Али ибн Сино-1</t>
+          <t>Чиланзар-26</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>41.334773</v>
+        <v>41.274511</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>69.164872</v>
+        <v>69.174975</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>41.334773, 69.164872</t>
+          <t>41.274511, 69.174975</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334773,69.164872</t>
+          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5189,14 +5189,14 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>запретная</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -5215,11 +5215,11 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 376 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5244,33 +5244,33 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Ташкент, 26-Й Квартал 30</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Чиланзар-26</t>
+          <t>Юнусабад-8</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>41.274511</v>
+        <v>41.368767</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>69.174975</v>
+        <v>69.27860200000001</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>41.274511, 69.174975</t>
+          <t>41.368767, 69.278602</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274511,69.174975</t>
+          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 120 м</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 375 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5324,43 +5324,43 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Юнусабадский р-н, 4-й кв-л, 47</t>
+          <t>массив Чиланзар, 14-й кв-л, 25</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Юнусабад-8</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>41.368767</v>
+        <v>41.297736</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>69.27860200000001</v>
+        <v>69.19082899999999</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>41.368767, 69.278602</t>
+          <t>41.297736, 69.190829</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368767,69.278602</t>
+          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>да: 120 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 370 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 368 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5424,45 +5424,45 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>массив Чиланзар, 14-й кв-л, 25</t>
+          <t>Ташкент, улица Катта Олмос, 21</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>Алмаслык</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>41.297736</v>
+        <v>41.271981</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>69.19082899999999</v>
+        <v>69.368154</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>41.297736, 69.190829</t>
+          <t>41.271981, 69.368154</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.297736,69.190829</t>
+          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 368 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5504,55 +5504,55 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ташкент, улица Катта Олмос, 21</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Алмаслык</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>41.271981</v>
+        <v>41.344107</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>69.368154</v>
+        <v>69.209092</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>41.271981, 69.368154</t>
+          <t>41.344107, 69.209092</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271981,69.368154</t>
+          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 283 м</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 365 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5604,33 +5604,33 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Фараби, 400</t>
+          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Бирлашган махалля</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>41.344107</v>
+        <v>41.295273</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>69.209092</v>
+        <v>69.35441400000001</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>41.344107, 69.209092</t>
+          <t>41.295273, 69.354414</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.344107,69.209092</t>
+          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>да: 283 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 364 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5694,33 +5694,33 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Ташкент, 1-Й Проезд Чулпон 1</t>
+          <t>Ташкент Малая Кольцевая Дорога 19</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Бирлашган махалля</t>
+          <t>Чимбай махалля</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41.295273</v>
+        <v>41.3491</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>69.35441400000001</v>
+        <v>69.216686</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>41.295273, 69.354414</t>
+          <t>41.349100, 69.216686</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.295273,69.354414</t>
+          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 50 м</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 362 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -5777,52 +5777,52 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Ташкент Малая Кольцевая Дорога 19</t>
+          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Чимбай махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>41.3491</v>
+        <v>41.284162</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>69.216686</v>
+        <v>69.35999099999999</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>41.349100, 69.216686</t>
+          <t>41.284162, 69.359991</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349100,69.216686</t>
+          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>да: 50 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -5849,12 +5849,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 361 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -5867,52 +5867,52 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, Ахангаранский проспект, 31</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Чиланзар-16</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41.284162</v>
+        <v>41.272128</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>69.35999099999999</v>
+        <v>69.200819</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>41.284162, 69.359991</t>
+          <t>41.272128, 69.200819</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284162,69.359991</t>
+          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5935,16 +5935,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 351 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -5954,55 +5954,55 @@
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 16-й кв-л, 27</t>
+          <t>Ташкент, 2-й квартал, 18</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Чиланзар-16</t>
+          <t>Тузель-2</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>41.272128</v>
+        <v>41.291661</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>69.200819</v>
+        <v>69.36116</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>41.272128, 69.200819</t>
+          <t>41.291661, 69.361160</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272128,69.200819</t>
+          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 344 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6044,43 +6044,43 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Ташкент, 2-й квартал, 18</t>
+          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Тузель-2</t>
+          <t>Чигатай-Актепа махалля</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>41.291661</v>
+        <v>41.349977</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>69.36116</v>
+        <v>69.190336</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>41.291661, 69.361160</t>
+          <t>41.349977, 69.190336</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291661,69.361160</t>
+          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 339 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6137,49 +6137,49 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Фараби, 402А</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа махалля</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>41.349977</v>
+        <v>41.337068</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>69.190336</v>
+        <v>69.285428</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>41.349977, 69.190336</t>
+          <t>41.337068, 69.285428</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349977,69.190336</t>
+          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 46 м</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 337 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 336 м</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6234,33 +6234,33 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, пр-кт Амира Темура, 96</t>
+          <t>Ташкент, улица Бабура 67/1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Минор (Ц-6)</t>
+          <t>Бабур</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>41.337068</v>
+        <v>41.280974</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>69.285428</v>
+        <v>69.258222</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>41.337068, 69.285428</t>
+          <t>41.280974, 69.258222</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337068,69.285428</t>
+          <t>https://www.google.com/maps?q=41.280974,69.258222</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>да: 46 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 336 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6324,33 +6324,33 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ташкент, улица Бабура 67/1</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Бабур</t>
+          <t>Риёзи (Чизельный)</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41.280974</v>
+        <v>41.314418</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>69.258222</v>
+        <v>69.32381700000001</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>41.280974, 69.258222</t>
+          <t>41.314418, 69.323817</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.280974,69.258222</t>
+          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 335 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6414,33 +6414,33 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Паркент, 74</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>Геофизика</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>41.314418</v>
+        <v>41.338894</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>69.32381700000001</v>
+        <v>69.386939</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>41.314418, 69.323817</t>
+          <t>41.338894, 69.386939</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314418,69.323817</t>
+          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -6479,12 +6479,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 330 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6497,52 +6497,52 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Мирзо-Улугбекский р-н, ул. Геофизика, 74</t>
+          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Геофизика</t>
+          <t>Сергели</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>41.338894</v>
+        <v>41.214477</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>69.386939</v>
+        <v>69.212414</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>41.338894, 69.386939</t>
+          <t>41.214477, 69.212414</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.338894,69.386939</t>
+          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 323 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 322 м</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Яндекс Маркет</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -6587,52 +6587,52 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Ташкент, Ташкент, улица Мирзы Турсунзаде, 1A</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 19-й кв-л, 31</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Сергели</t>
+          <t>Чиланзар-19</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>41.214477</v>
+        <v>41.269818</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>69.212414</v>
+        <v>69.184703</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>41.214477, 69.212414</t>
+          <t>41.269818, 69.184703</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214477,69.212414</t>
+          <t>https://www.google.com/maps?q=41.269818,69.184703</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 322 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6684,33 +6684,33 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 19-й кв-л, 31</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Чиланзар-19</t>
+          <t>Куйлюк Центр</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>41.269818</v>
+        <v>41.24192</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>69.184703</v>
+        <v>69.33096</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>41.269818, 69.184703</t>
+          <t>41.241920, 69.330960</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.269818,69.184703</t>
+          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 321 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -6764,17 +6764,17 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Ферганское ш., 1</t>
+          <t>Ташкент, массив Аханграбо, 8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6784,23 +6784,23 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>41.24192</v>
+        <v>41.252678</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>69.33096</v>
+        <v>69.344067</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>41.241920, 69.330960</t>
+          <t>41.252678, 69.344067</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241920,69.330960</t>
+          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>да: 175 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 315 м</t>
+          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6864,45 +6864,45 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Ташкент, массив Аханграбо, 8</t>
+          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Чиланзар-18</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>41.252678</v>
+        <v>41.274182</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>69.344067</v>
+        <v>69.190247</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>41.252678, 69.344067</t>
+          <t>41.274182, 69.190247</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252678,69.344067</t>
+          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="S72" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1 бренд (Ozon), 1 точка; ближайший Uzum в 309 м; точки только из Яндекс Карт — проверить</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 309 м</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Wildberries</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -6944,17 +6944,17 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Ташкент, массив Чиланзар, 18-й квартал, 15</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 3-й кв-л, 53</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6964,35 +6964,35 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Чиланзар-18</t>
+          <t>Чиланзар-3</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41.274182</v>
+        <v>41.283594</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>69.190247</v>
+        <v>69.22244600000001</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>41.274182, 69.190247</t>
+          <t>41.283594, 69.222446</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.274182,69.190247</t>
+          <t>https://www.google.com/maps?q=41.283594,69.222446</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="R73" t="n">
         <v>309</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 309 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 3-й кв-л, 53</t>
+          <t>Ташкент, 8-Й Квартал 1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7054,23 +7054,23 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Чиланзар-3</t>
+          <t>Чиланзар-6</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>41.283594</v>
+        <v>41.287081</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>69.22244600000001</v>
+        <v>69.205814</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>41.283594, 69.222446</t>
+          <t>41.287081, 69.205814</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283594,69.222446</t>
+          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7134,33 +7134,33 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Ташкент, 8-Й Квартал 1</t>
+          <t>Ташкент, улица Буюк Ипак Йули 77</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Чиланзар-6</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>41.287081</v>
+        <v>41.326369</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>69.205814</v>
+        <v>69.32475700000001</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>41.287081, 69.205814</t>
+          <t>41.326369, 69.324757</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7169,10 +7169,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7224,33 +7224,33 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Ташкент, улица Буюк Ипак Йули 77</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>41.326369</v>
+        <v>41.235793</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>69.32475700000001</v>
+        <v>69.352153</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>41.326369, 69.324757</t>
+          <t>41.235793, 69.352153</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -7307,52 +7307,48 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Сергели-6А</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>41.235793</v>
+        <v>41.230149</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>69.352153</v>
+        <v>69.206614</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>41.235793, 69.352153</t>
+          <t>41.230149, 69.206614</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
+          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="S77" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7361,7 +7357,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 9 м</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7370,94 +7366,8 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="n">
-        <v>20</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Яндекс Маркет</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Сергели-6А</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>41.230149</v>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>69.206614</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>41.230149, 69.206614</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R78" t="n">
-        <v>302</v>
-      </c>
-      <c r="S78" t="n">
-        <v>8</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>да: 9 м</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V78"/>
+  <autoFilter ref="A1:V77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -1985,7 +1985,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>да: 269 м</t>
+          <t>да: 139 м</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>да: 224 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 1613 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 1655 м</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>1613</v>
+        <v>1655</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>рекомендуемая</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>да: 0 м</t>
+          <t>да: 82 м</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -6906,7 +6906,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>запретная</t>
+          <t>белая</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">

--- a/data/competitor_gaps.xlsx
+++ b/data/competitor_gaps.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Конкуренты без Uzum" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Конкуренты без Uzum'!$A$1:$V$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V77"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -998,7 +998,7 @@
         <v>514</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 213 м</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>белая</t>
+          <t>рекомендуемая</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>да: 82 м</t>
+          <t>да: 0 м</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>да: 1 м</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4566,7 +4566,7 @@
         <v>400</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 309 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, Чиланзарский р-н, 3-й кв-л, 53</t>
+          <t>Ташкент, 8-Й Квартал 1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6964,23 +6964,23 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Чиланзар-3</t>
+          <t>Чиланзар-6</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41.283594</v>
+        <v>41.287081</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>69.22244600000001</v>
+        <v>69.205814</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>41.283594, 69.222446</t>
+          <t>41.287081, 69.205814</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283594,69.222446</t>
+          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 308 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7044,33 +7044,33 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Ташкент, 8-Й Квартал 1</t>
+          <t>Ташкент, улица Буюк Ипак Йули 77</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Чиланзар-6</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>41.287081</v>
+        <v>41.326369</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>69.205814</v>
+        <v>69.32475700000001</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>41.287081, 69.205814</t>
+          <t>41.326369, 69.324757</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287081,69.205814</t>
+          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 307 м</t>
+          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7134,33 +7134,33 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Ташкент, улица Буюк Ипак Йули 77</t>
+          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>41.326369</v>
+        <v>41.235793</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>69.32475700000001</v>
+        <v>69.352153</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>41.326369, 69.324757</t>
+          <t>41.235793, 69.352153</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.326369,69.324757</t>
+          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7169,10 +7169,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1 бренд (Wildberries), 1 точка; ближайший Uzum в 306 м</t>
+          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Wildberries</t>
+          <t>Яндекс Маркет</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -7217,52 +7217,48 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Узбекистан, Ташкент, г. Ташкент, ул. Юкори Чирчик, 64</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Бектемирский район</t>
-        </is>
-      </c>
+          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Сергели-6А</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>41.235793</v>
+        <v>41.230149</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>69.352153</v>
+        <v>69.206614</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>41.235793, 69.352153</t>
+          <t>41.230149, 69.206614</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.235793,69.352153</t>
+          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7271,7 +7267,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да: 9 м</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7280,94 +7276,8 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="n">
-        <v>20</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1 бренд (Яндекс Маркет), 1 точка; ближайший Uzum в 302 м; точки только из Яндекс Карт — проверить</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Яндекс Маркет</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Ташкент, Сергелийский район, Ташкент, массив Сергели-VIа, 77</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Сергели-6А</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>41.230149</v>
-      </c>
-      <c r="N77" s="2" t="n">
-        <v>69.206614</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>41.230149, 69.206614</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=41.230149,69.206614</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="R77" t="n">
-        <v>302</v>
-      </c>
-      <c r="S77" t="n">
-        <v>8</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>запретная</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>да: 9 м</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V77"/>
+  <autoFilter ref="A1:V76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>